--- a/lista_carros.xlsx
+++ b/lista_carros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EFEFD9-B701-446F-8372-835C64A856F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA602549-F4DA-40D6-844F-20C0C3FC7B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26904" yWindow="5796" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="661">
   <si>
     <t>Marca</t>
   </si>
@@ -2022,6 +2022,9 @@
   </si>
   <si>
     <t>V9</t>
+  </si>
+  <si>
+    <t>ZNegociar com a concessionária</t>
   </si>
 </sst>
 </file>
@@ -2471,7 +2474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{267EA263-FE3E-4242-9730-8BDC2B4FBB5D}">
-  <dimension ref="A1:P551"/>
+  <dimension ref="A1:P552"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -14029,6 +14032,23 @@
         <v>309900</v>
       </c>
     </row>
+    <row r="552" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A552" t="s">
+        <v>660</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C552" t="s">
+        <v>357</v>
+      </c>
+      <c r="D552" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="E552" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P356" xr:uid="{267EA263-FE3E-4242-9730-8BDC2B4FBB5D}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P549">

--- a/lista_carros.xlsx
+++ b/lista_carros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA602549-F4DA-40D6-844F-20C0C3FC7B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B81EAD0-D355-4D76-9561-A45E675F8D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26904" yWindow="5796" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2024,7 +2024,7 @@
     <t>V9</t>
   </si>
   <si>
-    <t>ZNegociar com a concessionária</t>
+    <t>Negociar com a concessionária</t>
   </si>
 </sst>
 </file>

--- a/lista_carros.xlsx
+++ b/lista_carros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077AAE7A-85A5-419A-A452-B2CA5571B2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775CF4D4-4B8C-430B-A8F6-965B384E2F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26904" yWindow="5796" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2330" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="661">
   <si>
     <t>Marca</t>
   </si>
@@ -620,15 +620,9 @@
     <t>Shark</t>
   </si>
   <si>
-    <t>Sealion</t>
-  </si>
-  <si>
     <t>Han</t>
   </si>
   <si>
-    <t>ATTO</t>
-  </si>
-  <si>
     <t>Tan</t>
   </si>
   <si>
@@ -2025,6 +2019,12 @@
   </si>
   <si>
     <t>Negociar com a concessionária</t>
+  </si>
+  <si>
+    <t>Sealion 7</t>
+  </si>
+  <si>
+    <t>ATTO 8</t>
   </si>
 </sst>
 </file>
@@ -2106,7 +2106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2139,6 +2139,7 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -2514,13 +2515,13 @@
         <v>55</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>302</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>304</v>
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -2830,7 +2831,7 @@
         <v>449990</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -2850,7 +2851,7 @@
         <v>479990</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2870,7 +2871,7 @@
         <v>629990</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2890,12 +2891,12 @@
         <v>644990</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C20" t="s">
         <v>41</v>
@@ -2910,12 +2911,12 @@
         <v>495950</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>451</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>455</v>
       </c>
       <c r="C21" t="s">
         <v>41</v>
@@ -2930,15 +2931,15 @@
         <v>383950</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C22" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D22" s="3">
         <v>2026</v>
@@ -2950,15 +2951,15 @@
         <v>859950</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C23" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D23" s="3">
         <v>2026</v>
@@ -2970,15 +2971,15 @@
         <v>330950</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C24" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D24" s="3">
         <v>2026</v>
@@ -2990,15 +2991,15 @@
         <v>539950</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C25" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D25" s="3">
         <v>2026</v>
@@ -3010,15 +3011,15 @@
         <v>410950</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D26" s="3">
         <v>2026</v>
@@ -3030,15 +3031,15 @@
         <v>645950</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C27" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D27" s="3">
         <v>2026</v>
@@ -3050,15 +3051,15 @@
         <v>515950</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C28" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D28" s="3">
         <v>2026</v>
@@ -3070,15 +3071,15 @@
         <v>887950</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C29" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D29" s="3">
         <v>2026</v>
@@ -3090,15 +3091,15 @@
         <v>1026950</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C30" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D30" s="3">
         <v>2026</v>
@@ -3106,19 +3107,20 @@
       <c r="E30" t="s">
         <v>17</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="1">
         <v>459950</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="8"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B31" s="10">
         <v>220</v>
       </c>
       <c r="C31" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D31" s="3">
         <v>2026</v>
@@ -3130,15 +3132,15 @@
         <v>332950</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C32" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D32" s="3">
         <v>2026</v>
@@ -3152,13 +3154,13 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C33" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D33" s="3">
         <v>2026</v>
@@ -3172,10 +3174,10 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C34" t="s">
         <v>22</v>
@@ -3192,10 +3194,10 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C35" t="s">
         <v>22</v>
@@ -3212,13 +3214,13 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C36" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D36" s="3">
         <v>2026</v>
@@ -3229,16 +3231,17 @@
       <c r="F36" s="1">
         <v>354950</v>
       </c>
+      <c r="H36" s="14"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C37" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D37" s="3">
         <v>2026</v>
@@ -3252,13 +3255,13 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C38" s="9" t="s">
         <v>478</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>480</v>
       </c>
       <c r="D38" s="3">
         <v>2026</v>
@@ -3272,13 +3275,13 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C39" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D39" s="3">
         <v>2026</v>
@@ -3292,13 +3295,13 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C40" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D40" s="3">
         <v>2026</v>
@@ -3312,10 +3315,10 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C41" t="s">
         <v>58</v>
@@ -3332,13 +3335,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C42" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D42" s="3">
         <v>2026</v>
@@ -3355,10 +3358,10 @@
         <v>28</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C43">
-        <v>8</v>
+        <v>660</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>355</v>
       </c>
       <c r="D43" s="3">
         <v>2026</v>
@@ -3375,10 +3378,10 @@
         <v>28</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C44" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D44" s="3">
         <v>2026</v>
@@ -3437,7 +3440,7 @@
         <v>28</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C47" t="s">
         <v>57</v>
@@ -3458,7 +3461,7 @@
         <v>28</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C48" t="s">
         <v>57</v>
@@ -3524,7 +3527,7 @@
         <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D51" s="3">
         <v>2026</v>
@@ -3584,10 +3587,10 @@
         <v>28</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C54">
-        <v>7</v>
+        <v>659</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>355</v>
       </c>
       <c r="D54" s="3">
         <v>2026</v>
@@ -3608,7 +3611,7 @@
         <v>33</v>
       </c>
       <c r="C55" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D55" s="3">
         <v>2026</v>
@@ -3629,7 +3632,7 @@
         <v>191</v>
       </c>
       <c r="C56" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D56" s="3">
         <v>2026</v>
@@ -3647,10 +3650,10 @@
         <v>28</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C57" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D57" s="3">
         <v>2025</v>
@@ -3668,10 +3671,10 @@
         <v>28</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C58" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D58" s="3">
         <v>2026</v>
@@ -3689,10 +3692,10 @@
         <v>28</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C59" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D59" s="3">
         <v>2026</v>
@@ -3725,7 +3728,7 @@
         <v>174990</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O60" s="1"/>
     </row>
@@ -3736,7 +3739,7 @@
       <c r="B61" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="12">
         <v>11</v>
       </c>
       <c r="D61" s="3">
@@ -3770,7 +3773,7 @@
         <v>149990</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O62" s="1"/>
     </row>
@@ -3794,7 +3797,7 @@
         <v>126990</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O63" s="1"/>
     </row>
@@ -3818,7 +3821,7 @@
         <v>146990</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O64" s="1"/>
     </row>
@@ -3842,7 +3845,7 @@
         <v>147990</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O65" s="1"/>
     </row>
@@ -3866,7 +3869,7 @@
         <v>184990</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O66" s="1"/>
     </row>
@@ -3890,7 +3893,7 @@
         <v>189990</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O67" s="1"/>
     </row>
@@ -3914,7 +3917,7 @@
         <v>181990</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="O68" s="1"/>
     </row>
@@ -3938,7 +3941,7 @@
         <v>189990</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O69" s="1"/>
     </row>
@@ -3962,7 +3965,7 @@
         <v>181990</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O70" s="1"/>
     </row>
@@ -3971,7 +3974,7 @@
         <v>37</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C71" t="s">
         <v>41</v>
@@ -3995,10 +3998,10 @@
         <v>37</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C72" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D72" s="3">
         <v>2026</v>
@@ -4070,7 +4073,7 @@
         <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D75" s="3">
         <v>2026</v>
@@ -4082,7 +4085,7 @@
         <v>101790</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
@@ -4093,7 +4096,7 @@
         <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D76" s="3">
         <v>2026</v>
@@ -4105,7 +4108,7 @@
         <v>109990</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
@@ -4116,7 +4119,7 @@
         <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D77" s="3">
         <v>2026</v>
@@ -4128,7 +4131,7 @@
         <v>114990</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
@@ -4151,7 +4154,7 @@
         <v>120990</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
@@ -4162,7 +4165,7 @@
         <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D79" s="3">
         <v>2026</v>
@@ -4174,7 +4177,7 @@
         <v>126190</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
@@ -4185,7 +4188,7 @@
         <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D80" s="3">
         <v>2026</v>
@@ -4197,7 +4200,7 @@
         <v>132390</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
@@ -4208,7 +4211,7 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D81" s="3">
         <v>2026</v>
@@ -4220,7 +4223,7 @@
         <v>133390</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
@@ -4231,7 +4234,7 @@
         <v>146</v>
       </c>
       <c r="C82" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D82" s="3">
         <v>2026</v>
@@ -4243,7 +4246,7 @@
         <v>108990</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
@@ -4254,7 +4257,7 @@
         <v>146</v>
       </c>
       <c r="C83" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D83" s="3">
         <v>2026</v>
@@ -4266,7 +4269,7 @@
         <v>115990</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
@@ -4277,7 +4280,7 @@
         <v>146</v>
       </c>
       <c r="C84" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D84" s="3">
         <v>2026</v>
@@ -4289,7 +4292,7 @@
         <v>121190</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
@@ -4300,7 +4303,7 @@
         <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D85" s="3">
         <v>2026</v>
@@ -4312,7 +4315,7 @@
         <v>126390</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
@@ -4323,7 +4326,7 @@
         <v>146</v>
       </c>
       <c r="C86" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D86" s="3">
         <v>2026</v>
@@ -4335,7 +4338,7 @@
         <v>132390</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
@@ -4346,7 +4349,7 @@
         <v>146</v>
       </c>
       <c r="C87" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D87" s="3">
         <v>2026</v>
@@ -4358,7 +4361,7 @@
         <v>139390</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
@@ -4381,7 +4384,7 @@
         <v>315000</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
@@ -4392,7 +4395,7 @@
         <v>89</v>
       </c>
       <c r="C89" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D89" s="3">
         <v>2026</v>
@@ -4404,7 +4407,7 @@
         <v>119990</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
@@ -4427,7 +4430,7 @@
         <v>145490</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
@@ -4438,7 +4441,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D91" s="3">
         <v>2026</v>
@@ -4450,7 +4453,7 @@
         <v>160790</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
@@ -4461,7 +4464,7 @@
         <v>89</v>
       </c>
       <c r="C92" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D92" s="3">
         <v>2026</v>
@@ -4473,7 +4476,7 @@
         <v>177990</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
@@ -4484,7 +4487,7 @@
         <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D93" s="3">
         <v>2026</v>
@@ -4496,7 +4499,7 @@
         <v>178990</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
@@ -4504,10 +4507,10 @@
         <v>37</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C94" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D94" s="3">
         <v>2026</v>
@@ -4519,7 +4522,7 @@
         <v>291190</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O94" s="1"/>
     </row>
@@ -4528,10 +4531,10 @@
         <v>37</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C95" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D95" s="3">
         <v>2026</v>
@@ -4543,7 +4546,7 @@
         <v>291190</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O95" s="1"/>
     </row>
@@ -4552,10 +4555,10 @@
         <v>37</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C96" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D96" s="3">
         <v>2027</v>
@@ -4567,7 +4570,7 @@
         <v>422590</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -4575,10 +4578,10 @@
         <v>37</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C97" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D97" s="3">
         <v>2027</v>
@@ -4590,7 +4593,7 @@
         <v>131990</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4598,7 +4601,7 @@
         <v>37</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C98" t="s">
         <v>90</v>
@@ -4613,7 +4616,7 @@
         <v>137690</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -4621,10 +4624,10 @@
         <v>37</v>
       </c>
       <c r="B99" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C99" t="s">
         <v>344</v>
-      </c>
-      <c r="C99" t="s">
-        <v>346</v>
       </c>
       <c r="D99" s="3">
         <v>2027</v>
@@ -4636,7 +4639,7 @@
         <v>154990</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -4644,10 +4647,10 @@
         <v>37</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C100" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D100" s="3">
         <v>2027</v>
@@ -4659,7 +4662,7 @@
         <v>162990</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -4667,10 +4670,10 @@
         <v>37</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C101" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D101" s="3">
         <v>2027</v>
@@ -4682,7 +4685,7 @@
         <v>167990</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4690,10 +4693,10 @@
         <v>37</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C102" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D102" s="3">
         <v>2027</v>
@@ -4705,7 +4708,7 @@
         <v>129990</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -4713,10 +4716,10 @@
         <v>37</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C103" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D103" s="3">
         <v>2027</v>
@@ -4728,7 +4731,7 @@
         <v>135990</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
@@ -4736,10 +4739,10 @@
         <v>37</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C104" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D104" s="3">
         <v>2027</v>
@@ -4751,7 +4754,7 @@
         <v>119990</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -4759,10 +4762,10 @@
         <v>37</v>
       </c>
       <c r="B105" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C105" t="s">
         <v>338</v>
-      </c>
-      <c r="C105" t="s">
-        <v>340</v>
       </c>
       <c r="D105" s="3">
         <v>2027</v>
@@ -4774,7 +4777,7 @@
         <v>138590</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
@@ -4782,7 +4785,7 @@
         <v>37</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C106" t="s">
         <v>52</v>
@@ -4797,7 +4800,7 @@
         <v>153990</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
@@ -4805,10 +4808,10 @@
         <v>37</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C107" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D107" s="3">
         <v>2027</v>
@@ -4820,7 +4823,7 @@
         <v>165590</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -4828,10 +4831,10 @@
         <v>37</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C108" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D108" s="3">
         <v>2026</v>
@@ -4843,7 +4846,7 @@
         <v>483990</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -4894,7 +4897,7 @@
         <v>87</v>
       </c>
       <c r="C111" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D111" s="3">
         <v>2027</v>
@@ -4914,7 +4917,7 @@
         <v>87</v>
       </c>
       <c r="C112" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D112" s="3">
         <v>2027</v>
@@ -4926,7 +4929,7 @@
         <v>304590</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
@@ -4937,7 +4940,7 @@
         <v>87</v>
       </c>
       <c r="C113" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D113" s="3">
         <v>2027</v>
@@ -4949,7 +4952,7 @@
         <v>285890</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
@@ -4960,7 +4963,7 @@
         <v>87</v>
       </c>
       <c r="C114" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D114" s="3">
         <v>2027</v>
@@ -4980,7 +4983,7 @@
         <v>92</v>
       </c>
       <c r="C115" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D115" s="3">
         <v>2026</v>
@@ -4992,7 +4995,7 @@
         <v>87450</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -5003,7 +5006,7 @@
         <v>92</v>
       </c>
       <c r="C116" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D116" s="3">
         <v>2026</v>
@@ -5015,7 +5018,7 @@
         <v>93590</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -5026,7 +5029,7 @@
         <v>92</v>
       </c>
       <c r="C117" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D117" s="3">
         <v>2026</v>
@@ -5038,7 +5041,7 @@
         <v>97590</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
@@ -5049,7 +5052,7 @@
         <v>92</v>
       </c>
       <c r="C118" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D118" s="3">
         <v>2026</v>
@@ -5061,7 +5064,7 @@
         <v>100590</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -5072,7 +5075,7 @@
         <v>92</v>
       </c>
       <c r="C119" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D119" s="3">
         <v>2026</v>
@@ -5084,7 +5087,7 @@
         <v>112590</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
@@ -5095,7 +5098,7 @@
         <v>93</v>
       </c>
       <c r="C120" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D120" s="3">
         <v>2026</v>
@@ -5107,7 +5110,7 @@
         <v>119990</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
@@ -5118,7 +5121,7 @@
         <v>93</v>
       </c>
       <c r="C121" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D121" s="3">
         <v>2026</v>
@@ -5130,7 +5133,7 @@
         <v>123790</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
@@ -5141,7 +5144,7 @@
         <v>93</v>
       </c>
       <c r="C122" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D122" s="3">
         <v>2026</v>
@@ -5153,7 +5156,7 @@
         <v>131790</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
@@ -5164,7 +5167,7 @@
         <v>93</v>
       </c>
       <c r="C123" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D123" s="3">
         <v>2026</v>
@@ -5176,7 +5179,7 @@
         <v>134790</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
@@ -5184,10 +5187,10 @@
         <v>91</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C124" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D124" s="3">
         <v>2026</v>
@@ -5199,7 +5202,7 @@
         <v>97690</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
@@ -5207,10 +5210,10 @@
         <v>91</v>
       </c>
       <c r="B125" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C125" t="s">
         <v>212</v>
-      </c>
-      <c r="C125" t="s">
-        <v>214</v>
       </c>
       <c r="D125" s="3">
         <v>2026</v>
@@ -5222,7 +5225,7 @@
         <v>112690</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
@@ -5230,10 +5233,10 @@
         <v>91</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C126" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D126" s="3">
         <v>2026</v>
@@ -5245,7 +5248,7 @@
         <v>117990</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
@@ -5253,10 +5256,10 @@
         <v>91</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C127" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D127" s="3">
         <v>2026</v>
@@ -5268,7 +5271,7 @@
         <v>119690</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
@@ -5279,7 +5282,7 @@
         <v>95</v>
       </c>
       <c r="C128" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D128" s="3">
         <v>2026</v>
@@ -5291,7 +5294,7 @@
         <v>96980</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
@@ -5302,7 +5305,7 @@
         <v>95</v>
       </c>
       <c r="C129" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D129" s="3">
         <v>2026</v>
@@ -5314,7 +5317,7 @@
         <v>97990</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -5325,7 +5328,7 @@
         <v>95</v>
       </c>
       <c r="C130" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D130" s="3">
         <v>2026</v>
@@ -5337,7 +5340,7 @@
         <v>109980</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
@@ -5348,7 +5351,7 @@
         <v>95</v>
       </c>
       <c r="C131" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D131" s="3">
         <v>2026</v>
@@ -5360,7 +5363,7 @@
         <v>103990</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
@@ -5371,7 +5374,7 @@
         <v>95</v>
       </c>
       <c r="C132" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D132" s="3">
         <v>2026</v>
@@ -5383,7 +5386,7 @@
         <v>112980</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -5391,10 +5394,10 @@
         <v>94</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C133" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D133" s="3">
         <v>2026</v>
@@ -5406,7 +5409,7 @@
         <v>109990</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
@@ -5414,10 +5417,10 @@
         <v>94</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C134" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D134" s="3">
         <v>2026</v>
@@ -5429,7 +5432,7 @@
         <v>114990</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
@@ -5437,10 +5440,10 @@
         <v>94</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C135" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D135" s="3">
         <v>2026</v>
@@ -5452,7 +5455,7 @@
         <v>121980</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -5460,10 +5463,10 @@
         <v>94</v>
       </c>
       <c r="B136" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C136" t="s">
         <v>378</v>
-      </c>
-      <c r="C136" t="s">
-        <v>380</v>
       </c>
       <c r="D136" s="3">
         <v>2026</v>
@@ -5475,7 +5478,7 @@
         <v>127980</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
@@ -5486,7 +5489,7 @@
         <v>96</v>
       </c>
       <c r="C137" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D137" s="3">
         <v>2026</v>
@@ -5498,7 +5501,7 @@
         <v>119990</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
@@ -5509,7 +5512,7 @@
         <v>96</v>
       </c>
       <c r="C138" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D138" s="3">
         <v>2026</v>
@@ -5521,7 +5524,7 @@
         <v>167490</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -5532,7 +5535,7 @@
         <v>96</v>
       </c>
       <c r="C139" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D139" s="3">
         <v>2026</v>
@@ -5544,7 +5547,7 @@
         <v>173490</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -5555,7 +5558,7 @@
         <v>96</v>
       </c>
       <c r="C140" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D140" s="3">
         <v>2026</v>
@@ -5567,7 +5570,7 @@
         <v>177990</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -5578,7 +5581,7 @@
         <v>96</v>
       </c>
       <c r="C141" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D141" s="3">
         <v>2026</v>
@@ -5590,7 +5593,7 @@
         <v>184980</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -5613,7 +5616,7 @@
         <v>83490</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -5624,7 +5627,7 @@
         <v>97</v>
       </c>
       <c r="C143" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D143" s="3">
         <v>2026</v>
@@ -5636,7 +5639,7 @@
         <v>85990</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -5647,7 +5650,7 @@
         <v>99</v>
       </c>
       <c r="C144" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D144" s="3">
         <v>2026</v>
@@ -5659,7 +5662,7 @@
         <v>103990</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -5670,7 +5673,7 @@
         <v>99</v>
       </c>
       <c r="C145" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D145" s="3">
         <v>2026</v>
@@ -5682,7 +5685,7 @@
         <v>115990</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -5693,7 +5696,7 @@
         <v>99</v>
       </c>
       <c r="C146" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D146" s="3">
         <v>2026</v>
@@ -5705,7 +5708,7 @@
         <v>119990</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -5716,7 +5719,7 @@
         <v>99</v>
       </c>
       <c r="C147" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D147" s="3">
         <v>2026</v>
@@ -5728,7 +5731,7 @@
         <v>136990</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -5739,7 +5742,7 @@
         <v>99</v>
       </c>
       <c r="C148" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D148" s="3">
         <v>2026</v>
@@ -5751,7 +5754,7 @@
         <v>151490</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -5762,7 +5765,7 @@
         <v>99</v>
       </c>
       <c r="C149" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D149" s="3">
         <v>2026</v>
@@ -5774,7 +5777,7 @@
         <v>162490</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -5785,7 +5788,7 @@
         <v>100</v>
       </c>
       <c r="C150" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D150" s="3">
         <v>2026</v>
@@ -5797,7 +5800,7 @@
         <v>153990</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -5808,7 +5811,7 @@
         <v>100</v>
       </c>
       <c r="C151" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D151" s="3">
         <v>2026</v>
@@ -5820,7 +5823,7 @@
         <v>153990</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -5831,7 +5834,7 @@
         <v>100</v>
       </c>
       <c r="C152" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D152" s="3">
         <v>2026</v>
@@ -5843,7 +5846,7 @@
         <v>142490</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
@@ -5854,7 +5857,7 @@
         <v>100</v>
       </c>
       <c r="C153" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D153" s="3">
         <v>2026</v>
@@ -5866,7 +5869,7 @@
         <v>136490</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
@@ -5877,7 +5880,7 @@
         <v>100</v>
       </c>
       <c r="C154" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D154" s="3">
         <v>2026</v>
@@ -5889,7 +5892,7 @@
         <v>133490</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
@@ -5900,7 +5903,7 @@
         <v>100</v>
       </c>
       <c r="C155" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D155" s="3">
         <v>2026</v>
@@ -5912,7 +5915,7 @@
         <v>123990</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
@@ -5923,7 +5926,7 @@
         <v>100</v>
       </c>
       <c r="C156" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D156" s="3">
         <v>2026</v>
@@ -5935,7 +5938,7 @@
         <v>116990</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
@@ -5946,7 +5949,7 @@
         <v>101</v>
       </c>
       <c r="C157" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D157" s="3">
         <v>2026</v>
@@ -5958,7 +5961,7 @@
         <v>167490</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
@@ -5969,7 +5972,7 @@
         <v>101</v>
       </c>
       <c r="C158" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D158" s="3">
         <v>2026</v>
@@ -5981,7 +5984,7 @@
         <v>177490</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
@@ -5992,7 +5995,7 @@
         <v>101</v>
       </c>
       <c r="C159" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D159" s="3">
         <v>2026</v>
@@ -6004,7 +6007,7 @@
         <v>197490</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
@@ -6015,7 +6018,7 @@
         <v>101</v>
       </c>
       <c r="C160" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D160" s="3">
         <v>2026</v>
@@ -6027,7 +6030,7 @@
         <v>206490</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
@@ -6038,7 +6041,7 @@
         <v>101</v>
       </c>
       <c r="C161" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D161" s="3">
         <v>2026</v>
@@ -6050,7 +6053,7 @@
         <v>220490</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
@@ -6061,7 +6064,7 @@
         <v>101</v>
       </c>
       <c r="C162" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D162" s="3">
         <v>2026</v>
@@ -6073,7 +6076,7 @@
         <v>238490</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
@@ -6081,10 +6084,10 @@
         <v>94</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C163" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D163" s="3">
         <v>2026</v>
@@ -6096,7 +6099,7 @@
         <v>238490</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
@@ -6104,10 +6107,10 @@
         <v>94</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C164" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D164" s="3">
         <v>2026</v>
@@ -6119,7 +6122,7 @@
         <v>268490</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
@@ -6127,10 +6130,10 @@
         <v>94</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C165" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D165" s="3">
         <v>2026</v>
@@ -6142,7 +6145,7 @@
         <v>291990</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
@@ -6150,10 +6153,10 @@
         <v>94</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C166" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D166" s="3">
         <v>2022</v>
@@ -6170,13 +6173,13 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>279</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C167" t="s">
         <v>281</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C167" t="s">
-        <v>283</v>
       </c>
       <c r="D167" s="3">
         <v>2026</v>
@@ -6190,13 +6193,13 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C168" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D168" s="3">
         <v>2026</v>
@@ -6210,13 +6213,13 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C169" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D169" s="3">
         <v>2026</v>
@@ -6230,13 +6233,13 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B170" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C170" t="s">
         <v>286</v>
-      </c>
-      <c r="C170" t="s">
-        <v>288</v>
       </c>
       <c r="D170" s="3">
         <v>2026</v>
@@ -6250,13 +6253,13 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C171" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D171" s="3">
         <v>2025</v>
@@ -6270,13 +6273,13 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C172" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D172" s="3">
         <v>2026</v>
@@ -6290,13 +6293,13 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C173" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D173" s="3">
         <v>2026</v>
@@ -6310,13 +6313,13 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C174" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D174" s="3">
         <v>2026</v>
@@ -6330,13 +6333,13 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C175" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D175" s="3">
         <v>2026</v>
@@ -6350,13 +6353,13 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B176" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C176" t="s">
         <v>295</v>
-      </c>
-      <c r="C176" t="s">
-        <v>297</v>
       </c>
       <c r="D176" s="3">
         <v>2026</v>
@@ -6370,13 +6373,13 @@
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C177" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D177" s="3">
         <v>2026</v>
@@ -6390,13 +6393,13 @@
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C178" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D178" s="3">
         <v>2026</v>
@@ -6410,13 +6413,13 @@
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C179" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D179" s="3">
         <v>2027</v>
@@ -6430,13 +6433,13 @@
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C180" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D180" s="3">
         <v>2026</v>
@@ -6450,13 +6453,13 @@
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C181" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D181" s="3">
         <v>2026</v>
@@ -6488,7 +6491,7 @@
         <v>159990</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O182" s="1"/>
     </row>
@@ -6512,7 +6515,7 @@
         <v>139990</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O183" s="1"/>
     </row>
@@ -6536,7 +6539,7 @@
         <v>209990</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="O184" s="1"/>
     </row>
@@ -6560,7 +6563,7 @@
         <v>191990</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="O185" s="1"/>
     </row>
@@ -6809,7 +6812,7 @@
         <v>34</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C196" t="s">
         <v>19</v>
@@ -6833,7 +6836,7 @@
         <v>34</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C197" t="s">
         <v>36</v>
@@ -6857,7 +6860,7 @@
         <v>34</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C198" t="s">
         <v>19</v>
@@ -6872,7 +6875,7 @@
         <v>189990</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O198" s="1"/>
     </row>
@@ -6881,7 +6884,7 @@
         <v>34</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C199" t="s">
         <v>36</v>
@@ -6896,7 +6899,7 @@
         <v>209990</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O199" s="1"/>
     </row>
@@ -6905,7 +6908,7 @@
         <v>34</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C200" t="s">
         <v>155</v>
@@ -6920,7 +6923,7 @@
         <v>234990</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O200" s="1"/>
     </row>
@@ -6929,10 +6932,10 @@
         <v>102</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C201" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D201" s="3">
         <v>2026</v>
@@ -6950,10 +6953,10 @@
         <v>102</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C202" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D202" s="3">
         <v>2026</v>
@@ -6971,10 +6974,10 @@
         <v>102</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C203" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D203" s="3">
         <v>2026</v>
@@ -6992,10 +6995,10 @@
         <v>102</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C204" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D204" s="3">
         <v>2026</v>
@@ -7013,10 +7016,10 @@
         <v>102</v>
       </c>
       <c r="B205" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C205" t="s">
         <v>411</v>
-      </c>
-      <c r="C205" t="s">
-        <v>413</v>
       </c>
       <c r="D205" s="3">
         <v>2026</v>
@@ -7034,10 +7037,10 @@
         <v>102</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C206" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D206" s="3">
         <v>2026</v>
@@ -7079,7 +7082,7 @@
         <v>103</v>
       </c>
       <c r="C208" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D208" s="3">
         <v>2026</v>
@@ -7100,7 +7103,7 @@
         <v>103</v>
       </c>
       <c r="C209" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D209" s="3">
         <v>2026</v>
@@ -7141,7 +7144,7 @@
         <v>103</v>
       </c>
       <c r="C211" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D211" s="3">
         <v>2026</v>
@@ -7161,7 +7164,7 @@
         <v>105</v>
       </c>
       <c r="C212" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D212" s="3">
         <v>2026</v>
@@ -7178,7 +7181,7 @@
         <v>102</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C213" t="s">
         <v>62</v>
@@ -7198,7 +7201,7 @@
         <v>106</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C214" t="s">
         <v>109</v>
@@ -7218,10 +7221,10 @@
         <v>106</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C215" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D215" s="3">
         <v>2026</v>
@@ -7238,7 +7241,7 @@
         <v>106</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C216" t="s">
         <v>51</v>
@@ -7258,7 +7261,7 @@
         <v>106</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C217" t="s">
         <v>108</v>
@@ -7278,10 +7281,10 @@
         <v>106</v>
       </c>
       <c r="B218" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C218" t="s">
         <v>366</v>
-      </c>
-      <c r="C218" t="s">
-        <v>368</v>
       </c>
       <c r="D218" s="3">
         <v>2026</v>
@@ -7298,10 +7301,10 @@
         <v>106</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C219" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D219" s="3">
         <v>2026</v>
@@ -7361,7 +7364,7 @@
         <v>107</v>
       </c>
       <c r="C222" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D222" s="3">
         <v>2026</v>
@@ -7381,7 +7384,7 @@
         <v>107</v>
       </c>
       <c r="C223" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D223" s="3">
         <v>2026</v>
@@ -7421,7 +7424,7 @@
         <v>50</v>
       </c>
       <c r="C225" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D225" s="3">
         <v>2026</v>
@@ -7501,7 +7504,7 @@
         <v>110</v>
       </c>
       <c r="C229" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D229" s="3">
         <v>2026</v>
@@ -7518,7 +7521,7 @@
         <v>106</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C230" t="s">
         <v>108</v>
@@ -7538,10 +7541,10 @@
         <v>106</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C231" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D231" s="3">
         <v>2026</v>
@@ -7558,7 +7561,7 @@
         <v>106</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C232" t="s">
         <v>109</v>
@@ -7578,10 +7581,10 @@
         <v>106</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C233" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D233" s="3">
         <v>2026</v>
@@ -7601,7 +7604,7 @@
         <v>112</v>
       </c>
       <c r="C234" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D234" s="3">
         <v>2026</v>
@@ -7621,7 +7624,7 @@
         <v>112</v>
       </c>
       <c r="C235" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D235" s="3">
         <v>2026</v>
@@ -7641,7 +7644,7 @@
         <v>112</v>
       </c>
       <c r="C236" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D236" s="3">
         <v>2026</v>
@@ -7661,7 +7664,7 @@
         <v>112</v>
       </c>
       <c r="C237" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D237" s="3">
         <v>2026</v>
@@ -7678,10 +7681,10 @@
         <v>111</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C238" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D238" s="3">
         <v>2026</v>
@@ -7698,10 +7701,10 @@
         <v>111</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C239" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D239" s="3">
         <v>2026</v>
@@ -7718,10 +7721,10 @@
         <v>111</v>
       </c>
       <c r="B240" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C240" t="s">
         <v>425</v>
-      </c>
-      <c r="C240" t="s">
-        <v>427</v>
       </c>
       <c r="D240" s="3">
         <v>2026</v>
@@ -7741,7 +7744,7 @@
         <v>113</v>
       </c>
       <c r="C241" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D241" s="3">
         <v>2026</v>
@@ -7761,7 +7764,7 @@
         <v>113</v>
       </c>
       <c r="C242" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D242" s="3">
         <v>2026</v>
@@ -7781,7 +7784,7 @@
         <v>113</v>
       </c>
       <c r="C243" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D243" s="3">
         <v>2026</v>
@@ -7801,7 +7804,7 @@
         <v>113</v>
       </c>
       <c r="C244" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D244" s="3">
         <v>2026</v>
@@ -7821,7 +7824,7 @@
         <v>114</v>
       </c>
       <c r="C245" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D245" s="3">
         <v>2026</v>
@@ -7841,7 +7844,7 @@
         <v>114</v>
       </c>
       <c r="C246" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D246" s="3">
         <v>2026</v>
@@ -7861,7 +7864,7 @@
         <v>114</v>
       </c>
       <c r="C247" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D247" s="3">
         <v>2026</v>
@@ -7881,7 +7884,7 @@
         <v>114</v>
       </c>
       <c r="C248" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D248" s="3">
         <v>2026</v>
@@ -7898,10 +7901,10 @@
         <v>111</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C249" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D249" s="3">
         <v>2026</v>
@@ -7918,10 +7921,10 @@
         <v>111</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C250" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D250" s="3">
         <v>2025</v>
@@ -7935,13 +7938,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
+        <v>644</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="C251" t="s">
         <v>646</v>
-      </c>
-      <c r="B251" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="C251" t="s">
-        <v>648</v>
       </c>
       <c r="D251" s="3">
         <v>2025</v>
@@ -7955,13 +7958,13 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B252" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="C252" t="s">
         <v>647</v>
-      </c>
-      <c r="C252" t="s">
-        <v>649</v>
       </c>
       <c r="D252" s="3">
         <v>2025</v>
@@ -7975,13 +7978,13 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C253" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D253" s="3">
         <v>2025</v>
@@ -7995,13 +7998,13 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C254" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D254" s="3">
         <v>2025</v>
@@ -8015,13 +8018,13 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C255" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D255" s="3">
         <v>2026</v>
@@ -8035,13 +8038,13 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C256" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D256" s="3">
         <v>2026</v>
@@ -8055,13 +8058,13 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C257" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D257" s="3">
         <v>2026</v>
@@ -8075,13 +8078,13 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C258" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D258" s="3">
         <v>2026</v>
@@ -8155,13 +8158,13 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
+        <v>560</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C262" t="s">
         <v>562</v>
-      </c>
-      <c r="B262" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="C262" t="s">
-        <v>564</v>
       </c>
       <c r="D262" s="3">
         <v>2024</v>
@@ -8175,13 +8178,13 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C263" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D263" s="3">
         <v>2024</v>
@@ -8195,13 +8198,13 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B264" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C264" s="11" t="s">
         <v>566</v>
-      </c>
-      <c r="C264" s="11" t="s">
-        <v>568</v>
       </c>
       <c r="D264" s="3">
         <v>2024</v>
@@ -8215,13 +8218,13 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C265" s="11" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D265" s="3">
         <v>2024</v>
@@ -8235,13 +8238,13 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C266" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D266" s="3">
         <v>2024</v>
@@ -8255,13 +8258,13 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C267" s="11" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D267" s="3">
         <v>2024</v>
@@ -8278,10 +8281,10 @@
         <v>115</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C268" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D268" s="3">
         <v>2027</v>
@@ -8301,7 +8304,7 @@
         <v>120</v>
       </c>
       <c r="C269" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D269" s="3">
         <v>2027</v>
@@ -8321,7 +8324,7 @@
         <v>120</v>
       </c>
       <c r="C270" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D270" s="3">
         <v>2026</v>
@@ -8333,7 +8336,7 @@
         <v>175990</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -8344,7 +8347,7 @@
         <v>120</v>
       </c>
       <c r="C271" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D271" s="3">
         <v>2027</v>
@@ -8356,7 +8359,7 @@
         <v>158990</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -8367,7 +8370,7 @@
         <v>120</v>
       </c>
       <c r="C272" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D272" s="3">
         <v>2026</v>
@@ -8407,7 +8410,7 @@
         <v>116</v>
       </c>
       <c r="C274" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D274" s="3">
         <v>2026</v>
@@ -8419,7 +8422,7 @@
         <v>255690</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -8430,7 +8433,7 @@
         <v>116</v>
       </c>
       <c r="C275" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D275" s="3">
         <v>2026</v>
@@ -8442,7 +8445,7 @@
         <v>283790</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -8453,7 +8456,7 @@
         <v>116</v>
       </c>
       <c r="C276" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D276" s="3">
         <v>2026</v>
@@ -8493,7 +8496,7 @@
         <v>117</v>
       </c>
       <c r="C278" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D278" s="3">
         <v>2026</v>
@@ -8505,7 +8508,7 @@
         <v>174990</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -8528,7 +8531,7 @@
         <v>201490</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -8539,7 +8542,7 @@
         <v>117</v>
       </c>
       <c r="C280" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D280" s="3">
         <v>2026</v>
@@ -8551,7 +8554,7 @@
         <v>233990</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -8562,7 +8565,7 @@
         <v>117</v>
       </c>
       <c r="C281" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D281" s="3">
         <v>2026</v>
@@ -8574,7 +8577,7 @@
         <v>278990</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -8582,10 +8585,10 @@
         <v>115</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C282" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D282" s="3">
         <v>2026</v>
@@ -8602,10 +8605,10 @@
         <v>115</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C283" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D283" s="3">
         <v>2026</v>
@@ -8662,7 +8665,7 @@
         <v>79</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C286" t="s">
         <v>81</v>
@@ -8682,7 +8685,7 @@
         <v>79</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C287" t="s">
         <v>26</v>
@@ -8702,7 +8705,7 @@
         <v>79</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C288" t="s">
         <v>81</v>
@@ -8722,7 +8725,7 @@
         <v>79</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C289" t="s">
         <v>26</v>
@@ -8739,13 +8742,13 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C290" s="11" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D290" s="3">
         <v>2026</v>
@@ -8759,13 +8762,13 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
+        <v>592</v>
+      </c>
+      <c r="B291" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="B291" s="4" t="s">
-        <v>596</v>
-      </c>
       <c r="C291" s="11" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D291" s="3">
         <v>2026</v>
@@ -8779,13 +8782,13 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
+        <v>592</v>
+      </c>
+      <c r="B292" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="B292" s="4" t="s">
+      <c r="C292" s="11" t="s">
         <v>596</v>
-      </c>
-      <c r="C292" s="11" t="s">
-        <v>598</v>
       </c>
       <c r="D292" s="3">
         <v>2026</v>
@@ -8799,13 +8802,13 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C293" s="11" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D293" s="3">
         <v>2026</v>
@@ -8819,13 +8822,13 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D294" s="3">
         <v>2025</v>
@@ -8839,13 +8842,13 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C295" s="11" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D295" s="3">
         <v>2026</v>
@@ -8859,13 +8862,13 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D296" s="3">
         <v>2026</v>
@@ -8879,13 +8882,13 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C297" s="11" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D297" s="3">
         <v>2027</v>
@@ -8899,13 +8902,13 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D298" s="3">
         <v>2027</v>
@@ -8919,13 +8922,13 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C299" s="11" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D299" s="3">
         <v>2027</v>
@@ -8939,13 +8942,13 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
+        <v>619</v>
+      </c>
+      <c r="B300" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="B300" s="4" t="s">
-        <v>623</v>
-      </c>
       <c r="C300" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D300" s="3">
         <v>2026</v>
@@ -8959,13 +8962,13 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D301" s="3">
         <v>2026</v>
@@ -8979,13 +8982,13 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D302" s="3">
         <v>2026</v>
@@ -8999,13 +9002,13 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D303" s="3">
         <v>2026</v>
@@ -9019,13 +9022,13 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
+        <v>619</v>
+      </c>
+      <c r="B304" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="B304" s="4" t="s">
-        <v>623</v>
-      </c>
       <c r="C304" s="12" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D304" s="3">
         <v>2026</v>
@@ -9039,13 +9042,13 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
+        <v>619</v>
+      </c>
+      <c r="B305" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="B305" s="4" t="s">
-        <v>623</v>
-      </c>
       <c r="C305" s="12" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D305" s="3">
         <v>2026</v>
@@ -9059,13 +9062,13 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C306" s="12" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D306" s="3">
         <v>2026</v>
@@ -9079,13 +9082,13 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C307" s="12" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D307" s="3">
         <v>2026</v>
@@ -9099,13 +9102,13 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C308" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D308" s="3">
         <v>2026</v>
@@ -9119,13 +9122,13 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D309" s="3">
         <v>2026</v>
@@ -9139,13 +9142,13 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C310" s="12" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D310" s="3">
         <v>2026</v>
@@ -9159,13 +9162,13 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D311" s="3">
         <v>2026</v>
@@ -9179,13 +9182,13 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
+        <v>401</v>
+      </c>
+      <c r="B312" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="B312" s="4" t="s">
-        <v>405</v>
-      </c>
       <c r="C312" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D312" s="3">
         <v>2026</v>
@@ -9199,13 +9202,13 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B313" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C313" t="s">
         <v>404</v>
-      </c>
-      <c r="C313" t="s">
-        <v>406</v>
       </c>
       <c r="D313" s="3">
         <v>2026</v>
@@ -9219,13 +9222,13 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C314" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D314" s="3">
         <v>2026</v>
@@ -9239,13 +9242,13 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
+        <v>607</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="C315" s="11" t="s">
         <v>609</v>
-      </c>
-      <c r="B315" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="C315" s="11" t="s">
-        <v>611</v>
       </c>
       <c r="D315" s="3">
         <v>2026</v>
@@ -9259,13 +9262,13 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C316" s="11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D316" s="3">
         <v>2026</v>
@@ -9279,13 +9282,13 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D317" s="3">
         <v>2026</v>
@@ -9299,13 +9302,13 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B318" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="C318" s="11" t="s">
         <v>613</v>
-      </c>
-      <c r="C318" s="11" t="s">
-        <v>615</v>
       </c>
       <c r="D318" s="3">
         <v>2026</v>
@@ -9319,13 +9322,13 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C319" s="11" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D319" s="3">
         <v>2026</v>
@@ -9339,13 +9342,13 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B320" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C320" s="11" t="s">
         <v>616</v>
-      </c>
-      <c r="C320" s="11" t="s">
-        <v>618</v>
       </c>
       <c r="D320" s="3">
         <v>2026</v>
@@ -9359,13 +9362,13 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C321" s="11" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D321" s="3">
         <v>2026</v>
@@ -9379,13 +9382,13 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C322" s="11" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D322" s="3">
         <v>2026</v>
@@ -9399,13 +9402,13 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
+        <v>607</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="C323" s="11" t="s">
         <v>609</v>
-      </c>
-      <c r="B323" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="C323" s="11" t="s">
-        <v>611</v>
       </c>
       <c r="D323" s="3">
         <v>2026</v>
@@ -9419,13 +9422,13 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C324" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D324" s="3">
         <v>2026</v>
@@ -9439,13 +9442,13 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
+        <v>575</v>
+      </c>
+      <c r="B325" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B325" s="4" t="s">
-        <v>579</v>
-      </c>
       <c r="C325" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D325" s="3">
         <v>2026</v>
@@ -9459,13 +9462,13 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C326" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D326" s="3">
         <v>2026</v>
@@ -9479,13 +9482,13 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C327" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D327" s="3">
         <v>2026</v>
@@ -9499,13 +9502,13 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C328" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D328" s="3">
         <v>2026</v>
@@ -9519,13 +9522,13 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C329" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D329" s="3">
         <v>2026</v>
@@ -9539,13 +9542,13 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C330" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D330" s="3">
         <v>2026</v>
@@ -9559,13 +9562,13 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C331" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D331" s="3">
         <v>2026</v>
@@ -9579,13 +9582,13 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B332" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C332" t="s">
         <v>521</v>
-      </c>
-      <c r="C332" t="s">
-        <v>523</v>
       </c>
       <c r="D332" s="3">
         <v>2026</v>
@@ -9599,13 +9602,13 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C333" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D333" s="3">
         <v>2026</v>
@@ -9619,13 +9622,13 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B334" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C334" t="s">
         <v>522</v>
-      </c>
-      <c r="C334" t="s">
-        <v>524</v>
       </c>
       <c r="D334" s="3">
         <v>2026</v>
@@ -9639,13 +9642,13 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C335" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D335" s="3">
         <v>2026</v>
@@ -9659,13 +9662,13 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C336" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D336" s="3">
         <v>2026</v>
@@ -9679,13 +9682,13 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C337" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D337" s="3">
         <v>2026</v>
@@ -9699,13 +9702,13 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
+        <v>534</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="C338" t="s">
         <v>536</v>
-      </c>
-      <c r="B338" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="C338" t="s">
-        <v>538</v>
       </c>
       <c r="D338" s="3">
         <v>2026</v>
@@ -9719,13 +9722,13 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C339" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D339" s="3">
         <v>2026</v>
@@ -9739,13 +9742,13 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C340" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D340" s="3">
         <v>2026</v>
@@ -9759,13 +9762,13 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C341" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D341" s="3">
         <v>2026</v>
@@ -9779,13 +9782,13 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C342" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D342" s="3">
         <v>2026</v>
@@ -9799,13 +9802,13 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C343" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D343" s="3">
         <v>2026</v>
@@ -9819,13 +9822,13 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C344" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D344" s="3">
         <v>2026</v>
@@ -9839,13 +9842,13 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B345" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C345" t="s">
         <v>512</v>
-      </c>
-      <c r="C345" t="s">
-        <v>514</v>
       </c>
       <c r="D345" s="3">
         <v>2026</v>
@@ -9859,13 +9862,13 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C346" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D346" s="3">
         <v>2026</v>
@@ -9879,13 +9882,13 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C347" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D347" s="3">
         <v>2026</v>
@@ -9899,13 +9902,13 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C348" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D348" s="3">
         <v>2026</v>
@@ -9919,13 +9922,13 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C349" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D349" s="3">
         <v>2026</v>
@@ -9939,13 +9942,13 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C350" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D350" s="3">
         <v>2026</v>
@@ -9959,13 +9962,13 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C351" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D351" s="3">
         <v>2026</v>
@@ -9979,13 +9982,13 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C352" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D352" s="3">
         <v>2026</v>
@@ -9999,13 +10002,13 @@
     </row>
     <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C353" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D353" s="3">
         <v>2026</v>
@@ -10019,13 +10022,13 @@
     </row>
     <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C354" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D354" s="3">
         <v>2026</v>
@@ -10039,13 +10042,13 @@
     </row>
     <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C355" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D355" s="3">
         <v>2026</v>
@@ -10059,13 +10062,13 @@
     </row>
     <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C356" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D356" s="3">
         <v>2026</v>
@@ -10079,13 +10082,13 @@
     </row>
     <row r="357" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C357" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D357" s="3">
         <v>2026</v>
@@ -10099,10 +10102,10 @@
     </row>
     <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C358" t="s">
         <v>12</v>
@@ -10119,13 +10122,13 @@
     </row>
     <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C359" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D359" s="3">
         <v>2026</v>
@@ -10139,13 +10142,13 @@
     </row>
     <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C360" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D360" s="3">
         <v>2026</v>
@@ -10246,7 +10249,7 @@
         <v>45</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C365" t="s">
         <v>47</v>
@@ -10267,7 +10270,7 @@
         <v>45</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C366" t="s">
         <v>44</v>
@@ -10288,10 +10291,10 @@
         <v>45</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C367" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D367" s="3">
         <v>2025</v>
@@ -10306,13 +10309,13 @@
     </row>
     <row r="368" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
+        <v>634</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C368" s="12" t="s">
         <v>636</v>
-      </c>
-      <c r="B368" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="C368" s="12" t="s">
-        <v>638</v>
       </c>
       <c r="D368" s="3">
         <v>2026</v>
@@ -10326,13 +10329,13 @@
     </row>
     <row r="369" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C369" s="12" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D369" s="3">
         <v>2026</v>
@@ -10346,13 +10349,13 @@
     </row>
     <row r="370" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B370" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="C370" s="12" t="s">
         <v>639</v>
-      </c>
-      <c r="C370" s="12" t="s">
-        <v>641</v>
       </c>
       <c r="D370" s="3">
         <v>2026</v>
@@ -10366,13 +10369,13 @@
     </row>
     <row r="371" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C371" s="12" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D371" s="3">
         <v>2026</v>
@@ -10386,13 +10389,13 @@
     </row>
     <row r="372" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C372" s="12" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D372" s="3">
         <v>2026</v>
@@ -10406,13 +10409,13 @@
     </row>
     <row r="373" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C373" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D373" s="3">
         <v>2026</v>
@@ -10426,13 +10429,13 @@
     </row>
     <row r="374" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B374" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C374" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D374" s="3">
         <v>2026</v>
@@ -10452,7 +10455,7 @@
         <v>6</v>
       </c>
       <c r="C375" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D375" s="3">
         <v>2027</v>
@@ -10473,7 +10476,7 @@
         <v>6</v>
       </c>
       <c r="C376" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D376" s="3">
         <v>2027</v>
@@ -10494,7 +10497,7 @@
         <v>6</v>
       </c>
       <c r="C377" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D377" s="3">
         <v>2027</v>
@@ -10515,7 +10518,7 @@
         <v>6</v>
       </c>
       <c r="C378" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D378" s="3">
         <v>2027</v>
@@ -10536,7 +10539,7 @@
         <v>6</v>
       </c>
       <c r="C379" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D379" s="3">
         <v>2027</v>
@@ -10557,7 +10560,7 @@
         <v>6</v>
       </c>
       <c r="C380" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D380" s="3">
         <v>2027</v>
@@ -10575,10 +10578,10 @@
         <v>5</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C381" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D381" s="3">
         <v>2026</v>
@@ -10596,10 +10599,10 @@
         <v>5</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C382" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D382" s="3">
         <v>2026</v>
@@ -10617,10 +10620,10 @@
         <v>5</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C383" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D383" s="3">
         <v>2027</v>
@@ -10638,10 +10641,10 @@
         <v>5</v>
       </c>
       <c r="B384" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C384" t="s">
         <v>323</v>
-      </c>
-      <c r="C384" t="s">
-        <v>325</v>
       </c>
       <c r="D384" s="3">
         <v>2027</v>
@@ -10659,10 +10662,10 @@
         <v>5</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C385" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D385" s="3">
         <v>2027</v>
@@ -10680,10 +10683,10 @@
         <v>5</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C386" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D386" s="3">
         <v>2027</v>
@@ -10701,10 +10704,10 @@
         <v>5</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C387" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D387" s="3">
         <v>2027</v>
@@ -10722,10 +10725,10 @@
         <v>5</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C388" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D388" s="3">
         <v>2027</v>
@@ -10743,10 +10746,10 @@
         <v>5</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C389" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D389" s="3">
         <v>2027</v>
@@ -10764,10 +10767,10 @@
         <v>5</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C390" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D390" s="3">
         <v>2027</v>
@@ -10785,10 +10788,10 @@
         <v>5</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C391" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D391" s="3">
         <v>2027</v>
@@ -11352,13 +11355,13 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C419" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D419" s="3">
         <v>2024</v>
@@ -11372,13 +11375,13 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C420" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D420" s="3">
         <v>2024</v>
@@ -11392,13 +11395,13 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C421" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D421" s="3">
         <v>2025</v>
@@ -11412,13 +11415,13 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C422" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D422" s="3">
         <v>2024</v>
@@ -11432,13 +11435,13 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C423" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D423" s="3">
         <v>2024</v>
@@ -11452,13 +11455,13 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C424" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D424" s="3">
         <v>2025</v>
@@ -11472,13 +11475,13 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C425" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D425" s="3">
         <v>2026</v>
@@ -11492,13 +11495,13 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B426" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C426" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D426" s="3">
         <v>2026</v>
@@ -11512,13 +11515,13 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
+        <v>485</v>
+      </c>
+      <c r="B427" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="C427" t="s">
         <v>487</v>
-      </c>
-      <c r="B427" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="C427" t="s">
-        <v>489</v>
       </c>
       <c r="D427" s="3">
         <v>2026</v>
@@ -11532,13 +11535,13 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B428" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C428" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D428" s="3">
         <v>2026</v>
@@ -11552,13 +11555,13 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B429" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C429" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D429" s="3">
         <v>2026</v>
@@ -11572,13 +11575,13 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B430" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C430" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D430" s="3">
         <v>2026</v>
@@ -11592,13 +11595,13 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B431" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C431" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D431" s="3">
         <v>2026</v>
@@ -11612,10 +11615,10 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C432" t="s">
         <v>13</v>
@@ -11632,13 +11635,13 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C433" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D433" s="3">
         <v>2026</v>
@@ -11652,13 +11655,13 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C434" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D434" s="3">
         <v>2027</v>
@@ -11672,13 +11675,13 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C435" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D435" s="3">
         <v>2027</v>
@@ -11692,13 +11695,13 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C436" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D436" s="3">
         <v>2026</v>
@@ -11712,13 +11715,13 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C437" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D437" s="3">
         <v>2026</v>
@@ -11732,13 +11735,13 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B438" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C438" t="s">
         <v>508</v>
-      </c>
-      <c r="C438" t="s">
-        <v>510</v>
       </c>
       <c r="D438" s="3">
         <v>2026</v>
@@ -11752,13 +11755,13 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C439" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D439" s="3">
         <v>2026</v>
@@ -11772,13 +11775,13 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C440" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D440" s="3">
         <v>2026</v>
@@ -11792,13 +11795,13 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
+        <v>580</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C441" s="11" t="s">
         <v>582</v>
-      </c>
-      <c r="B441" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="C441" s="11" t="s">
-        <v>584</v>
       </c>
       <c r="D441" s="3">
         <v>2026</v>
@@ -11812,13 +11815,13 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B442" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C442" s="11" t="s">
         <v>583</v>
-      </c>
-      <c r="C442" s="11" t="s">
-        <v>585</v>
       </c>
       <c r="D442" s="3">
         <v>2026</v>
@@ -11832,13 +11835,13 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C443" s="11" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D443" s="3">
         <v>2026</v>
@@ -11852,13 +11855,13 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C444" s="11" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D444" s="3">
         <v>2026</v>
@@ -11872,13 +11875,13 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B445" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="C445" s="11" t="s">
         <v>587</v>
-      </c>
-      <c r="C445" s="11" t="s">
-        <v>589</v>
       </c>
       <c r="D445" s="3">
         <v>2026</v>
@@ -11892,13 +11895,13 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C446" s="11" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D446" s="3">
         <v>2026</v>
@@ -11912,13 +11915,13 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C447" s="11" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D447" s="3">
         <v>2026</v>
@@ -11932,13 +11935,13 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C448" s="11" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D448" s="3">
         <v>2026</v>
@@ -11952,13 +11955,13 @@
     </row>
     <row r="449" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B449" s="10">
         <v>1500</v>
       </c>
       <c r="C449" s="11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D449" s="3">
         <v>2026</v>
@@ -11972,13 +11975,13 @@
     </row>
     <row r="450" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B450" s="10">
         <v>2500</v>
       </c>
       <c r="C450" s="11" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D450" s="3">
         <v>2026</v>
@@ -11992,13 +11995,13 @@
     </row>
     <row r="451" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B451" s="10">
         <v>3500</v>
       </c>
       <c r="C451" s="11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D451" s="3">
         <v>2026</v>
@@ -12012,13 +12015,13 @@
     </row>
     <row r="452" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B452" s="10">
         <v>3500</v>
       </c>
       <c r="C452" s="11" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D452" s="3">
         <v>2026</v>
@@ -12038,7 +12041,7 @@
         <v>70</v>
       </c>
       <c r="C453" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D453" s="3">
         <v>2026</v>
@@ -12080,7 +12083,7 @@
         <v>70</v>
       </c>
       <c r="C455" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D455" s="3">
         <v>2026</v>
@@ -12121,7 +12124,7 @@
         <v>124</v>
       </c>
       <c r="C457" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D457" s="3">
         <v>2026</v>
@@ -12141,7 +12144,7 @@
         <v>124</v>
       </c>
       <c r="C458" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D458" s="3">
         <v>2026</v>
@@ -12161,7 +12164,7 @@
         <v>124</v>
       </c>
       <c r="C459" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D459" s="3">
         <v>2026</v>
@@ -12181,7 +12184,7 @@
         <v>124</v>
       </c>
       <c r="C460" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D460" s="3">
         <v>2026</v>
@@ -12201,7 +12204,7 @@
         <v>125</v>
       </c>
       <c r="C461" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D461" s="3">
         <v>2026</v>
@@ -12221,7 +12224,7 @@
         <v>125</v>
       </c>
       <c r="C462" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D462" s="3">
         <v>2026</v>
@@ -12241,7 +12244,7 @@
         <v>125</v>
       </c>
       <c r="C463" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D463" s="3">
         <v>2026</v>
@@ -12281,7 +12284,7 @@
         <v>125</v>
       </c>
       <c r="C465" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D465" s="3">
         <v>2026</v>
@@ -12298,10 +12301,10 @@
         <v>69</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C466" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D466" s="3">
         <v>2026</v>
@@ -12321,7 +12324,7 @@
         <v>126</v>
       </c>
       <c r="C467" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D467" s="3">
         <v>2026</v>
@@ -12341,7 +12344,7 @@
         <v>126</v>
       </c>
       <c r="C468" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D468" s="3">
         <v>2026</v>
@@ -12361,7 +12364,7 @@
         <v>126</v>
       </c>
       <c r="C469" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D469" s="3">
         <v>2026</v>
@@ -12378,7 +12381,7 @@
         <v>69</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C470" t="s">
         <v>19</v>
@@ -12398,10 +12401,10 @@
         <v>69</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C471" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D471" s="3">
         <v>2026</v>
@@ -12418,10 +12421,10 @@
         <v>69</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C472" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D472" s="3">
         <v>2026</v>
@@ -12435,13 +12438,13 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
+        <v>572</v>
+      </c>
+      <c r="B473" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C473" s="11" t="s">
         <v>574</v>
-      </c>
-      <c r="B473" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="C473" s="11" t="s">
-        <v>576</v>
       </c>
       <c r="D473" s="3">
         <v>2026</v>
@@ -12455,13 +12458,13 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
+        <v>569</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C474" s="11" t="s">
         <v>571</v>
-      </c>
-      <c r="B474" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="C474" s="11" t="s">
-        <v>573</v>
       </c>
       <c r="D474" s="3">
         <v>2026</v>
@@ -12493,7 +12496,7 @@
         <v>177590</v>
       </c>
       <c r="G475" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.3">
@@ -12504,7 +12507,7 @@
         <v>128</v>
       </c>
       <c r="C476" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D476" s="3">
         <v>2026</v>
@@ -12516,7 +12519,7 @@
         <v>206790</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.3">
@@ -12527,7 +12530,7 @@
         <v>128</v>
       </c>
       <c r="C477" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D477" s="3">
         <v>2026</v>
@@ -12539,7 +12542,7 @@
         <v>194790</v>
       </c>
       <c r="G477" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.3">
@@ -12562,10 +12565,10 @@
         <v>210090</v>
       </c>
       <c r="G478" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.3">
@@ -12576,7 +12579,7 @@
         <v>128</v>
       </c>
       <c r="C479" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D479" s="3">
         <v>2026</v>
@@ -12588,7 +12591,7 @@
         <v>206790</v>
       </c>
       <c r="G479" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.3">
@@ -12599,7 +12602,7 @@
         <v>131</v>
       </c>
       <c r="C480" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D480" s="3">
         <v>2026</v>
@@ -12639,7 +12642,7 @@
         <v>131</v>
       </c>
       <c r="C482" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D482" s="3">
         <v>2026</v>
@@ -12679,7 +12682,7 @@
         <v>131</v>
       </c>
       <c r="C484" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D484" s="3">
         <v>2026</v>
@@ -12699,7 +12702,7 @@
         <v>134</v>
       </c>
       <c r="C485" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D485" s="3">
         <v>2026</v>
@@ -12719,7 +12722,7 @@
         <v>134</v>
       </c>
       <c r="C486" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D486" s="3">
         <v>2026</v>
@@ -12739,7 +12742,7 @@
         <v>134</v>
       </c>
       <c r="C487" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D487" s="3">
         <v>2026</v>
@@ -12759,7 +12762,7 @@
         <v>134</v>
       </c>
       <c r="C488" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D488" s="3">
         <v>2026</v>
@@ -12779,7 +12782,7 @@
         <v>134</v>
       </c>
       <c r="C489" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D489" s="3">
         <v>2026</v>
@@ -12799,7 +12802,7 @@
         <v>134</v>
       </c>
       <c r="C490" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D490" s="3">
         <v>2026</v>
@@ -12819,7 +12822,7 @@
         <v>134</v>
       </c>
       <c r="C491" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D491" s="3">
         <v>2026</v>
@@ -12839,7 +12842,7 @@
         <v>134</v>
       </c>
       <c r="C492" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D492" s="3">
         <v>2026</v>
@@ -12859,7 +12862,7 @@
         <v>134</v>
       </c>
       <c r="C493" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D493" s="3">
         <v>2026</v>
@@ -12879,7 +12882,7 @@
         <v>134</v>
       </c>
       <c r="C494" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D494" s="3">
         <v>2026</v>
@@ -12896,10 +12899,10 @@
         <v>127</v>
       </c>
       <c r="B495" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C495" t="s">
         <v>258</v>
-      </c>
-      <c r="C495" t="s">
-        <v>260</v>
       </c>
       <c r="D495" s="3">
         <v>2026</v>
@@ -12916,10 +12919,10 @@
         <v>127</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C496" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D496" s="3">
         <v>2026</v>
@@ -12939,7 +12942,7 @@
         <v>135</v>
       </c>
       <c r="C497" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D497" s="3">
         <v>2026</v>
@@ -12959,7 +12962,7 @@
         <v>135</v>
       </c>
       <c r="C498" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D498" s="3">
         <v>2026</v>
@@ -12999,7 +13002,7 @@
         <v>144</v>
       </c>
       <c r="C500" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D500" s="3">
         <v>2026</v>
@@ -13019,7 +13022,7 @@
         <v>144</v>
       </c>
       <c r="C501" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D501" s="3">
         <v>2026</v>
@@ -13039,7 +13042,7 @@
         <v>144</v>
       </c>
       <c r="C502" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D502" s="3">
         <v>2026</v>
@@ -13096,10 +13099,10 @@
         <v>127</v>
       </c>
       <c r="B505" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C505" t="s">
         <v>275</v>
-      </c>
-      <c r="C505" t="s">
-        <v>277</v>
       </c>
       <c r="D505" s="3">
         <v>2026</v>
@@ -13116,10 +13119,10 @@
         <v>127</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C506" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D506" s="3">
         <v>2026</v>
@@ -13136,10 +13139,10 @@
         <v>127</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C507" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D507" s="3">
         <v>2026</v>
@@ -13156,10 +13159,10 @@
         <v>127</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C508" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D508" s="3">
         <v>2026</v>
@@ -13200,7 +13203,7 @@
         <v>10</v>
       </c>
       <c r="C510" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D510" s="3">
         <v>2026</v>
@@ -13221,7 +13224,7 @@
         <v>10</v>
       </c>
       <c r="C511" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D511" s="3">
         <v>2026</v>
@@ -13284,7 +13287,7 @@
         <v>10</v>
       </c>
       <c r="C514" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D514" s="3">
         <v>2026</v>
@@ -13347,7 +13350,7 @@
         <v>68</v>
       </c>
       <c r="C517" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D517" s="3">
         <v>2026</v>
@@ -13367,7 +13370,7 @@
         <v>68</v>
       </c>
       <c r="C518" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D518" s="3">
         <v>2026</v>
@@ -13387,7 +13390,7 @@
         <v>68</v>
       </c>
       <c r="C519" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D519" s="3">
         <v>2026</v>
@@ -13407,7 +13410,7 @@
         <v>68</v>
       </c>
       <c r="C520" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D520" s="3">
         <v>2027</v>
@@ -13428,7 +13431,7 @@
         <v>68</v>
       </c>
       <c r="C521" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D521" s="3">
         <v>2027</v>
@@ -13469,7 +13472,7 @@
         <v>139</v>
       </c>
       <c r="C523" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D523" s="3">
         <v>2026</v>
@@ -13489,7 +13492,7 @@
         <v>139</v>
       </c>
       <c r="C524" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D524" s="3">
         <v>2026</v>
@@ -13509,7 +13512,7 @@
         <v>139</v>
       </c>
       <c r="C525" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D525" s="3">
         <v>2026</v>
@@ -13569,7 +13572,7 @@
         <v>141</v>
       </c>
       <c r="C528" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D528" s="3">
         <v>2026</v>
@@ -13606,7 +13609,7 @@
         <v>7</v>
       </c>
       <c r="B530" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C530" t="s">
         <v>47</v>
@@ -13626,10 +13629,10 @@
         <v>7</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C531" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D531" s="3">
         <v>2026</v>
@@ -13646,10 +13649,10 @@
         <v>7</v>
       </c>
       <c r="B532" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C532" t="s">
         <v>435</v>
-      </c>
-      <c r="C532" t="s">
-        <v>437</v>
       </c>
       <c r="D532" s="3">
         <v>2026</v>
@@ -13666,10 +13669,10 @@
         <v>7</v>
       </c>
       <c r="B533" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C533" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D533" s="3">
         <v>2026</v>
@@ -13686,10 +13689,10 @@
         <v>7</v>
       </c>
       <c r="B534" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C534" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D534" s="3">
         <v>2027</v>
@@ -13706,10 +13709,10 @@
         <v>7</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C535" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D535" s="3">
         <v>2026</v>
@@ -13726,10 +13729,10 @@
         <v>7</v>
       </c>
       <c r="B536" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C536" t="s">
         <v>448</v>
-      </c>
-      <c r="C536" t="s">
-        <v>450</v>
       </c>
       <c r="D536" s="3">
         <v>2026</v>
@@ -13746,10 +13749,10 @@
         <v>7</v>
       </c>
       <c r="B537" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C537" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D537" s="3">
         <v>2026</v>
@@ -13766,10 +13769,10 @@
         <v>7</v>
       </c>
       <c r="B538" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C538" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D538" s="3">
         <v>2026</v>
@@ -13783,13 +13786,13 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B539" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C539" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D539" s="3">
         <v>2026</v>
@@ -13803,13 +13806,13 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
+        <v>546</v>
+      </c>
+      <c r="B540" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="B540" s="4" t="s">
-        <v>550</v>
-      </c>
       <c r="C540" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D540" s="3">
         <v>2026</v>
@@ -13823,10 +13826,10 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B541" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C541" t="s">
         <v>41</v>
@@ -13843,10 +13846,10 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B542" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C542" t="s">
         <v>41</v>
@@ -13863,10 +13866,10 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B543" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C543" t="s">
         <v>41</v>
@@ -13883,10 +13886,10 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C544" t="s">
         <v>41</v>
@@ -13903,10 +13906,10 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B545" s="4" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C545" t="s">
         <v>41</v>
@@ -13923,13 +13926,13 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B546" s="10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C546" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D546" s="3">
         <v>2026</v>
@@ -13943,13 +13946,13 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C547" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D547" s="3">
         <v>2026</v>
@@ -13963,13 +13966,13 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B548" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C548" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D548" s="3">
         <v>2026</v>
@@ -13983,13 +13986,13 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
+        <v>654</v>
+      </c>
+      <c r="B549" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C549" t="s">
         <v>656</v>
-      </c>
-      <c r="B549" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="C549" t="s">
-        <v>658</v>
       </c>
       <c r="D549" s="3">
         <v>2027</v>
@@ -14003,13 +14006,13 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B550" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C550" t="s">
         <v>657</v>
-      </c>
-      <c r="C550" t="s">
-        <v>659</v>
       </c>
       <c r="D550" s="3">
         <v>2027</v>
@@ -14023,16 +14026,16 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B551" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C551" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E551" t="s">
         <v>17</v>

--- a/lista_carros.xlsx
+++ b/lista_carros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775CF4D4-4B8C-430B-A8F6-965B384E2F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299F3CD3-764C-423B-97E3-0A18E81299AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26904" yWindow="5796" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="661">
   <si>
     <t>Marca</t>
   </si>
@@ -1433,9 +1433,6 @@
     <t>xDrive</t>
   </si>
   <si>
-    <t>M Sport</t>
-  </si>
-  <si>
     <t>M235</t>
   </si>
   <si>
@@ -2025,6 +2022,9 @@
   </si>
   <si>
     <t>ATTO 8</t>
+  </si>
+  <si>
+    <t>220 M</t>
   </si>
 </sst>
 </file>
@@ -2106,7 +2106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2139,7 +2139,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -2959,7 +2958,7 @@
         <v>456</v>
       </c>
       <c r="C23" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D23" s="3">
         <v>2026</v>
@@ -2979,7 +2978,7 @@
         <v>457</v>
       </c>
       <c r="C24" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D24" s="3">
         <v>2026</v>
@@ -2999,7 +2998,7 @@
         <v>457</v>
       </c>
       <c r="C25" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D25" s="3">
         <v>2026</v>
@@ -3019,7 +3018,7 @@
         <v>458</v>
       </c>
       <c r="C26" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D26" s="3">
         <v>2026</v>
@@ -3039,7 +3038,7 @@
         <v>458</v>
       </c>
       <c r="C27" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D27" s="3">
         <v>2026</v>
@@ -3059,7 +3058,7 @@
         <v>459</v>
       </c>
       <c r="C28" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D28" s="3">
         <v>2026</v>
@@ -3079,7 +3078,7 @@
         <v>460</v>
       </c>
       <c r="C29" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D29" s="3">
         <v>2026</v>
@@ -3116,11 +3115,11 @@
       <c r="A31" t="s">
         <v>451</v>
       </c>
-      <c r="B31" s="10">
-        <v>220</v>
+      <c r="B31" s="10" t="s">
+        <v>660</v>
       </c>
       <c r="C31" t="s">
-        <v>463</v>
+        <v>58</v>
       </c>
       <c r="D31" s="3">
         <v>2026</v>
@@ -3137,7 +3136,7 @@
         <v>451</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C32" t="s">
         <v>462</v>
@@ -3157,10 +3156,10 @@
         <v>451</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C33" t="s">
         <v>465</v>
-      </c>
-      <c r="C33" t="s">
-        <v>466</v>
       </c>
       <c r="D33" s="3">
         <v>2026</v>
@@ -3177,7 +3176,7 @@
         <v>451</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C34" t="s">
         <v>22</v>
@@ -3197,7 +3196,7 @@
         <v>451</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C35" t="s">
         <v>22</v>
@@ -3217,10 +3216,10 @@
         <v>451</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C36" t="s">
         <v>474</v>
-      </c>
-      <c r="C36" t="s">
-        <v>475</v>
       </c>
       <c r="D36" s="3">
         <v>2026</v>
@@ -3231,17 +3230,16 @@
       <c r="F36" s="1">
         <v>354950</v>
       </c>
-      <c r="H36" s="14"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>451</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C37" t="s">
         <v>476</v>
-      </c>
-      <c r="C37" t="s">
-        <v>477</v>
       </c>
       <c r="D37" s="3">
         <v>2026</v>
@@ -3258,10 +3256,10 @@
         <v>451</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D38" s="3">
         <v>2026</v>
@@ -3278,10 +3276,10 @@
         <v>451</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C39" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D39" s="3">
         <v>2026</v>
@@ -3298,10 +3296,10 @@
         <v>451</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C40" t="s">
         <v>480</v>
-      </c>
-      <c r="C40" t="s">
-        <v>481</v>
       </c>
       <c r="D40" s="3">
         <v>2026</v>
@@ -3318,7 +3316,7 @@
         <v>451</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C41" t="s">
         <v>58</v>
@@ -3338,10 +3336,10 @@
         <v>451</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C42" t="s">
         <v>483</v>
-      </c>
-      <c r="C42" t="s">
-        <v>484</v>
       </c>
       <c r="D42" s="3">
         <v>2026</v>
@@ -3358,7 +3356,7 @@
         <v>28</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>355</v>
@@ -3587,7 +3585,7 @@
         <v>28</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>355</v>
@@ -7938,13 +7936,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
+        <v>643</v>
+      </c>
+      <c r="B251" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="C251" t="s">
         <v>645</v>
-      </c>
-      <c r="C251" t="s">
-        <v>646</v>
       </c>
       <c r="D251" s="3">
         <v>2025</v>
@@ -7958,13 +7956,13 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
+        <v>643</v>
+      </c>
+      <c r="B252" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="B252" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="C252" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D252" s="3">
         <v>2025</v>
@@ -7978,10 +7976,10 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C253" t="s">
         <v>355</v>
@@ -7998,10 +7996,10 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C254" t="s">
         <v>355</v>
@@ -8018,10 +8016,10 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C255" t="s">
         <v>305</v>
@@ -8038,10 +8036,10 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C256" t="s">
         <v>306</v>
@@ -8058,13 +8056,13 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C257" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D257" s="3">
         <v>2026</v>
@@ -8078,13 +8076,13 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C258" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D258" s="3">
         <v>2026</v>
@@ -8158,13 +8156,13 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
+        <v>559</v>
+      </c>
+      <c r="B262" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="B262" s="4" t="s">
+      <c r="C262" t="s">
         <v>561</v>
-      </c>
-      <c r="C262" t="s">
-        <v>562</v>
       </c>
       <c r="D262" s="3">
         <v>2024</v>
@@ -8178,13 +8176,13 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C263" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D263" s="3">
         <v>2024</v>
@@ -8198,13 +8196,13 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C264" s="11" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D264" s="3">
         <v>2024</v>
@@ -8218,13 +8216,13 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C265" s="11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D265" s="3">
         <v>2024</v>
@@ -8238,13 +8236,13 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B266" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C266" t="s">
         <v>564</v>
-      </c>
-      <c r="C266" t="s">
-        <v>565</v>
       </c>
       <c r="D266" s="3">
         <v>2024</v>
@@ -8258,13 +8256,13 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C267" s="11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D267" s="3">
         <v>2024</v>
@@ -8742,13 +8740,13 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
+        <v>591</v>
+      </c>
+      <c r="B290" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="B290" s="4" t="s">
-        <v>593</v>
-      </c>
       <c r="C290" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D290" s="3">
         <v>2026</v>
@@ -8762,13 +8760,13 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B291" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="C291" s="11" t="s">
         <v>594</v>
-      </c>
-      <c r="C291" s="11" t="s">
-        <v>595</v>
       </c>
       <c r="D291" s="3">
         <v>2026</v>
@@ -8782,13 +8780,13 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C292" s="11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D292" s="3">
         <v>2026</v>
@@ -8802,13 +8800,13 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B293" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="C293" s="11" t="s">
         <v>597</v>
-      </c>
-      <c r="C293" s="11" t="s">
-        <v>598</v>
       </c>
       <c r="D293" s="3">
         <v>2026</v>
@@ -8822,13 +8820,13 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B294" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C294" s="11" t="s">
         <v>599</v>
-      </c>
-      <c r="C294" s="11" t="s">
-        <v>600</v>
       </c>
       <c r="D294" s="3">
         <v>2025</v>
@@ -8842,13 +8840,13 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B295" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="C295" s="11" t="s">
         <v>601</v>
-      </c>
-      <c r="C295" s="11" t="s">
-        <v>602</v>
       </c>
       <c r="D295" s="3">
         <v>2026</v>
@@ -8862,13 +8860,13 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D296" s="3">
         <v>2026</v>
@@ -8882,13 +8880,13 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C297" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D297" s="3">
         <v>2027</v>
@@ -8902,13 +8900,13 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D298" s="3">
         <v>2027</v>
@@ -8922,13 +8920,13 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C299" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D299" s="3">
         <v>2027</v>
@@ -8942,13 +8940,13 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B300" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C300" t="s">
         <v>621</v>
-      </c>
-      <c r="C300" t="s">
-        <v>622</v>
       </c>
       <c r="D300" s="3">
         <v>2026</v>
@@ -8962,13 +8960,13 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D301" s="3">
         <v>2026</v>
@@ -8982,13 +8980,13 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D302" s="3">
         <v>2026</v>
@@ -9002,13 +9000,13 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D303" s="3">
         <v>2026</v>
@@ -9022,13 +9020,13 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B304" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C304" s="12" t="s">
         <v>621</v>
-      </c>
-      <c r="C304" s="12" t="s">
-        <v>622</v>
       </c>
       <c r="D304" s="3">
         <v>2026</v>
@@ -9042,13 +9040,13 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C305" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D305" s="3">
         <v>2026</v>
@@ -9062,13 +9060,13 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C306" s="12" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D306" s="3">
         <v>2026</v>
@@ -9082,13 +9080,13 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
+        <v>618</v>
+      </c>
+      <c r="B307" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="B307" s="4" t="s">
-        <v>620</v>
-      </c>
       <c r="C307" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D307" s="3">
         <v>2026</v>
@@ -9102,10 +9100,10 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
+        <v>618</v>
+      </c>
+      <c r="B308" s="4" t="s">
         <v>619</v>
-      </c>
-      <c r="B308" s="4" t="s">
-        <v>620</v>
       </c>
       <c r="C308" s="12" t="s">
         <v>310</v>
@@ -9122,13 +9120,13 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D309" s="3">
         <v>2026</v>
@@ -9142,13 +9140,13 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C310" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D310" s="3">
         <v>2026</v>
@@ -9162,13 +9160,13 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D311" s="3">
         <v>2026</v>
@@ -9242,13 +9240,13 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
+        <v>606</v>
+      </c>
+      <c r="B315" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="B315" s="4" t="s">
+      <c r="C315" s="11" t="s">
         <v>608</v>
-      </c>
-      <c r="C315" s="11" t="s">
-        <v>609</v>
       </c>
       <c r="D315" s="3">
         <v>2026</v>
@@ -9262,10 +9260,10 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C316" s="11" t="s">
         <v>399</v>
@@ -9282,13 +9280,13 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B317" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="C317" s="11" t="s">
         <v>611</v>
-      </c>
-      <c r="C317" s="11" t="s">
-        <v>612</v>
       </c>
       <c r="D317" s="3">
         <v>2026</v>
@@ -9302,13 +9300,13 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D318" s="3">
         <v>2026</v>
@@ -9322,13 +9320,13 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B319" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="C319" s="11" t="s">
         <v>614</v>
-      </c>
-      <c r="C319" s="11" t="s">
-        <v>615</v>
       </c>
       <c r="D319" s="3">
         <v>2026</v>
@@ -9342,13 +9340,13 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C320" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D320" s="3">
         <v>2026</v>
@@ -9362,13 +9360,13 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C321" s="11" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D321" s="3">
         <v>2026</v>
@@ -9382,13 +9380,13 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C322" s="11" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D322" s="3">
         <v>2026</v>
@@ -9402,13 +9400,13 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C323" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D323" s="3">
         <v>2026</v>
@@ -9422,10 +9420,10 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
+        <v>574</v>
+      </c>
+      <c r="B324" s="4" t="s">
         <v>575</v>
-      </c>
-      <c r="B324" s="4" t="s">
-        <v>576</v>
       </c>
       <c r="C324" s="11" t="s">
         <v>355</v>
@@ -9442,10 +9440,10 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C325" s="11" t="s">
         <v>355</v>
@@ -9462,10 +9460,10 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C326" s="11" t="s">
         <v>355</v>
@@ -9482,10 +9480,10 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C327" s="11" t="s">
         <v>355</v>
@@ -9502,13 +9500,13 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C328" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D328" s="3">
         <v>2026</v>
@@ -9522,13 +9520,13 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C329" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D329" s="3">
         <v>2026</v>
@@ -9542,13 +9540,13 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B330" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C330" t="s">
         <v>515</v>
-      </c>
-      <c r="C330" t="s">
-        <v>516</v>
       </c>
       <c r="D330" s="3">
         <v>2026</v>
@@ -9562,13 +9560,13 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B331" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C331" t="s">
         <v>517</v>
-      </c>
-      <c r="C331" t="s">
-        <v>518</v>
       </c>
       <c r="D331" s="3">
         <v>2026</v>
@@ -9582,13 +9580,13 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C332" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D332" s="3">
         <v>2026</v>
@@ -9602,13 +9600,13 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B333" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C333" t="s">
         <v>520</v>
-      </c>
-      <c r="C333" t="s">
-        <v>521</v>
       </c>
       <c r="D333" s="3">
         <v>2026</v>
@@ -9622,13 +9620,13 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C334" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D334" s="3">
         <v>2026</v>
@@ -9642,13 +9640,13 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B335" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C335" t="s">
         <v>523</v>
-      </c>
-      <c r="C335" t="s">
-        <v>524</v>
       </c>
       <c r="D335" s="3">
         <v>2026</v>
@@ -9662,13 +9660,13 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C336" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D336" s="3">
         <v>2026</v>
@@ -9682,13 +9680,13 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B337" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C337" t="s">
         <v>531</v>
-      </c>
-      <c r="C337" t="s">
-        <v>532</v>
       </c>
       <c r="D337" s="3">
         <v>2026</v>
@@ -9702,13 +9700,13 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
+        <v>533</v>
+      </c>
+      <c r="B338" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="B338" s="4" t="s">
+      <c r="C338" t="s">
         <v>535</v>
-      </c>
-      <c r="C338" t="s">
-        <v>536</v>
       </c>
       <c r="D338" s="3">
         <v>2026</v>
@@ -9722,13 +9720,13 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B339" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="C339" t="s">
         <v>537</v>
-      </c>
-      <c r="C339" t="s">
-        <v>538</v>
       </c>
       <c r="D339" s="3">
         <v>2026</v>
@@ -9742,13 +9740,13 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C340" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D340" s="3">
         <v>2026</v>
@@ -9762,13 +9760,13 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B341" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C341" t="s">
         <v>540</v>
-      </c>
-      <c r="C341" t="s">
-        <v>541</v>
       </c>
       <c r="D341" s="3">
         <v>2026</v>
@@ -9782,13 +9780,13 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B342" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="C342" t="s">
         <v>542</v>
-      </c>
-      <c r="C342" t="s">
-        <v>543</v>
       </c>
       <c r="D342" s="3">
         <v>2026</v>
@@ -9802,13 +9800,13 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B343" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="C343" t="s">
         <v>544</v>
-      </c>
-      <c r="C343" t="s">
-        <v>545</v>
       </c>
       <c r="D343" s="3">
         <v>2026</v>
@@ -9822,13 +9820,13 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B344" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C344" t="s">
         <v>510</v>
-      </c>
-      <c r="C344" t="s">
-        <v>511</v>
       </c>
       <c r="D344" s="3">
         <v>2026</v>
@@ -9842,13 +9840,13 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C345" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D345" s="3">
         <v>2026</v>
@@ -9862,13 +9860,13 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B346" s="4" t="s">
         <v>324</v>
       </c>
       <c r="C346" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D346" s="3">
         <v>2026</v>
@@ -9882,13 +9880,13 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C347" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D347" s="3">
         <v>2026</v>
@@ -9902,13 +9900,13 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C348" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D348" s="3">
         <v>2026</v>
@@ -9922,13 +9920,13 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C349" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D349" s="3">
         <v>2026</v>
@@ -9942,13 +9940,13 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C350" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D350" s="3">
         <v>2026</v>
@@ -9962,13 +9960,13 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C351" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D351" s="3">
         <v>2026</v>
@@ -9982,13 +9980,13 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C352" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D352" s="3">
         <v>2026</v>
@@ -10002,13 +10000,13 @@
     </row>
     <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C353" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D353" s="3">
         <v>2026</v>
@@ -10022,13 +10020,13 @@
     </row>
     <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C354" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D354" s="3">
         <v>2026</v>
@@ -10042,13 +10040,13 @@
     </row>
     <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C355" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D355" s="3">
         <v>2026</v>
@@ -10062,13 +10060,13 @@
     </row>
     <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C356" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D356" s="3">
         <v>2026</v>
@@ -10082,13 +10080,13 @@
     </row>
     <row r="357" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C357" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D357" s="3">
         <v>2026</v>
@@ -10102,10 +10100,10 @@
     </row>
     <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C358" t="s">
         <v>12</v>
@@ -10122,13 +10120,13 @@
     </row>
     <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C359" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D359" s="3">
         <v>2026</v>
@@ -10142,13 +10140,13 @@
     </row>
     <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C360" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D360" s="3">
         <v>2026</v>
@@ -10309,13 +10307,13 @@
     </row>
     <row r="368" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
+        <v>633</v>
+      </c>
+      <c r="B368" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="B368" s="4" t="s">
+      <c r="C368" s="12" t="s">
         <v>635</v>
-      </c>
-      <c r="C368" s="12" t="s">
-        <v>636</v>
       </c>
       <c r="D368" s="3">
         <v>2026</v>
@@ -10329,13 +10327,13 @@
     </row>
     <row r="369" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B369" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="C369" s="12" t="s">
         <v>637</v>
-      </c>
-      <c r="C369" s="12" t="s">
-        <v>638</v>
       </c>
       <c r="D369" s="3">
         <v>2026</v>
@@ -10349,13 +10347,13 @@
     </row>
     <row r="370" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C370" s="12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D370" s="3">
         <v>2026</v>
@@ -10369,13 +10367,13 @@
     </row>
     <row r="371" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C371" s="12" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D371" s="3">
         <v>2026</v>
@@ -10389,13 +10387,13 @@
     </row>
     <row r="372" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B372" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="C372" s="12" t="s">
         <v>641</v>
-      </c>
-      <c r="C372" s="12" t="s">
-        <v>642</v>
       </c>
       <c r="D372" s="3">
         <v>2026</v>
@@ -10409,10 +10407,10 @@
     </row>
     <row r="373" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C373" s="12" t="s">
         <v>355</v>
@@ -10429,7 +10427,7 @@
     </row>
     <row r="374" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B374" s="4" t="s">
         <v>41</v>
@@ -11355,13 +11353,13 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C419" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D419" s="3">
         <v>2024</v>
@@ -11375,13 +11373,13 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B420" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C420" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D420" s="3">
         <v>2024</v>
@@ -11395,13 +11393,13 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B421" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C421" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D421" s="3">
         <v>2025</v>
@@ -11415,13 +11413,13 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C422" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D422" s="3">
         <v>2024</v>
@@ -11435,13 +11433,13 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B423" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C423" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D423" s="3">
         <v>2024</v>
@@ -11455,13 +11453,13 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B424" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C424" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D424" s="3">
         <v>2025</v>
@@ -11475,13 +11473,13 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C425" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D425" s="3">
         <v>2026</v>
@@ -11495,13 +11493,13 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
+        <v>484</v>
+      </c>
+      <c r="B426" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="C426" t="s">
         <v>485</v>
-      </c>
-      <c r="B426" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="C426" t="s">
-        <v>486</v>
       </c>
       <c r="D426" s="3">
         <v>2026</v>
@@ -11515,13 +11513,13 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B427" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C427" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D427" s="3">
         <v>2026</v>
@@ -11535,13 +11533,13 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B428" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C428" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D428" s="3">
         <v>2026</v>
@@ -11555,13 +11553,13 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B429" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C429" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D429" s="3">
         <v>2026</v>
@@ -11575,13 +11573,13 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B430" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C430" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D430" s="3">
         <v>2026</v>
@@ -11595,13 +11593,13 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B431" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C431" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D431" s="3">
         <v>2026</v>
@@ -11615,10 +11613,10 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C432" t="s">
         <v>13</v>
@@ -11635,13 +11633,13 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B433" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C433" t="s">
         <v>488</v>
-      </c>
-      <c r="C433" t="s">
-        <v>489</v>
       </c>
       <c r="D433" s="3">
         <v>2026</v>
@@ -11655,13 +11653,13 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C434" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D434" s="3">
         <v>2027</v>
@@ -11675,13 +11673,13 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B435" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C435" t="s">
         <v>504</v>
-      </c>
-      <c r="C435" t="s">
-        <v>505</v>
       </c>
       <c r="D435" s="3">
         <v>2027</v>
@@ -11695,10 +11693,10 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C436" t="s">
         <v>355</v>
@@ -11715,13 +11713,13 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B437" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="C437" t="s">
         <v>506</v>
-      </c>
-      <c r="C437" t="s">
-        <v>507</v>
       </c>
       <c r="D437" s="3">
         <v>2026</v>
@@ -11735,13 +11733,13 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C438" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D438" s="3">
         <v>2026</v>
@@ -11755,13 +11753,13 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C439" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D439" s="3">
         <v>2026</v>
@@ -11775,13 +11773,13 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C440" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D440" s="3">
         <v>2026</v>
@@ -11795,13 +11793,13 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
+        <v>579</v>
+      </c>
+      <c r="B441" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="B441" s="4" t="s">
+      <c r="C441" s="11" t="s">
         <v>581</v>
-      </c>
-      <c r="C441" s="11" t="s">
-        <v>582</v>
       </c>
       <c r="D441" s="3">
         <v>2026</v>
@@ -11815,13 +11813,13 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
+        <v>579</v>
+      </c>
+      <c r="B442" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="B442" s="4" t="s">
-        <v>581</v>
-      </c>
       <c r="C442" s="11" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D442" s="3">
         <v>2026</v>
@@ -11835,13 +11833,13 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
+        <v>579</v>
+      </c>
+      <c r="B443" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="B443" s="4" t="s">
-        <v>581</v>
-      </c>
       <c r="C443" s="11" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D443" s="3">
         <v>2026</v>
@@ -11855,13 +11853,13 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B444" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="C444" s="11" t="s">
         <v>585</v>
-      </c>
-      <c r="C444" s="11" t="s">
-        <v>586</v>
       </c>
       <c r="D444" s="3">
         <v>2026</v>
@@ -11875,13 +11873,13 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C445" s="11" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D445" s="3">
         <v>2026</v>
@@ -11895,13 +11893,13 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C446" s="11" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D446" s="3">
         <v>2026</v>
@@ -11915,13 +11913,13 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C447" s="11" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D447" s="3">
         <v>2026</v>
@@ -11935,13 +11933,13 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C448" s="11" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D448" s="3">
         <v>2026</v>
@@ -11955,13 +11953,13 @@
     </row>
     <row r="449" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B449" s="10">
         <v>1500</v>
       </c>
       <c r="C449" s="11" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D449" s="3">
         <v>2026</v>
@@ -11975,13 +11973,13 @@
     </row>
     <row r="450" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B450" s="10">
         <v>2500</v>
       </c>
       <c r="C450" s="11" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D450" s="3">
         <v>2026</v>
@@ -11995,13 +11993,13 @@
     </row>
     <row r="451" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B451" s="10">
         <v>3500</v>
       </c>
       <c r="C451" s="11" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D451" s="3">
         <v>2026</v>
@@ -12015,13 +12013,13 @@
     </row>
     <row r="452" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B452" s="10">
         <v>3500</v>
       </c>
       <c r="C452" s="11" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D452" s="3">
         <v>2026</v>
@@ -12438,13 +12436,13 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
+        <v>571</v>
+      </c>
+      <c r="B473" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="B473" s="4" t="s">
+      <c r="C473" s="11" t="s">
         <v>573</v>
-      </c>
-      <c r="C473" s="11" t="s">
-        <v>574</v>
       </c>
       <c r="D473" s="3">
         <v>2026</v>
@@ -12458,13 +12456,13 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
+        <v>568</v>
+      </c>
+      <c r="B474" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="B474" s="4" t="s">
+      <c r="C474" s="11" t="s">
         <v>570</v>
-      </c>
-      <c r="C474" s="11" t="s">
-        <v>571</v>
       </c>
       <c r="D474" s="3">
         <v>2026</v>
@@ -13786,10 +13784,10 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
+        <v>545</v>
+      </c>
+      <c r="B539" s="4" t="s">
         <v>546</v>
-      </c>
-      <c r="B539" s="4" t="s">
-        <v>547</v>
       </c>
       <c r="C539" t="s">
         <v>455</v>
@@ -13806,10 +13804,10 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B540" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C540" t="s">
         <v>455</v>
@@ -13826,10 +13824,10 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B541" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C541" t="s">
         <v>41</v>
@@ -13846,10 +13844,10 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B542" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C542" t="s">
         <v>41</v>
@@ -13866,10 +13864,10 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B543" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C543" t="s">
         <v>41</v>
@@ -13886,10 +13884,10 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C544" t="s">
         <v>41</v>
@@ -13906,10 +13904,10 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B545" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C545" t="s">
         <v>41</v>
@@ -13926,10 +13924,10 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
+        <v>553</v>
+      </c>
+      <c r="B546" s="10" t="s">
         <v>554</v>
-      </c>
-      <c r="B546" s="10" t="s">
-        <v>555</v>
       </c>
       <c r="C546" t="s">
         <v>355</v>
@@ -13946,10 +13944,10 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C547" t="s">
         <v>355</v>
@@ -13966,10 +13964,10 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B548" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C548" t="s">
         <v>355</v>
@@ -13986,13 +13984,13 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
+        <v>653</v>
+      </c>
+      <c r="B549" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="B549" s="4" t="s">
+      <c r="C549" t="s">
         <v>655</v>
-      </c>
-      <c r="C549" t="s">
-        <v>656</v>
       </c>
       <c r="D549" s="3">
         <v>2027</v>
@@ -14006,13 +14004,13 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
+        <v>653</v>
+      </c>
+      <c r="B550" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="B550" s="4" t="s">
-        <v>655</v>
-      </c>
       <c r="C550" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D550" s="3">
         <v>2027</v>
@@ -14026,7 +14024,7 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B551" s="4" t="s">
         <v>355</v>

--- a/lista_carros.xlsx
+++ b/lista_carros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA503A9-C23C-4F1F-94C4-0F1DF318ACED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA17A73-0724-4DC4-A0EE-7D4DA9D4D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4992" yWindow="4992" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26388" yWindow="5220" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carros" sheetId="1" r:id="rId1"/>
@@ -191,9 +191,6 @@
     <t>Caoa Changan</t>
   </si>
   <si>
-    <t>Unit-T</t>
-  </si>
-  <si>
     <t>Civic</t>
   </si>
   <si>
@@ -2040,6 +2037,9 @@
   </si>
   <si>
     <t>Mako</t>
+  </si>
+  <si>
+    <t>Uni-T</t>
   </si>
 </sst>
 </file>
@@ -2529,22 +2529,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>301</v>
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -2562,7 +2562,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" s="3">
         <v>2025</v>
@@ -2579,7 +2579,7 @@
         <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -2599,10 +2599,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" t="s">
         <v>157</v>
-      </c>
-      <c r="C4" t="s">
-        <v>158</v>
       </c>
       <c r="D4" s="3">
         <v>2027</v>
@@ -2619,10 +2619,10 @@
         <v>20</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D5" s="3">
         <v>2027</v>
@@ -2642,7 +2642,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D6" s="3">
         <v>2027</v>
@@ -2659,7 +2659,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
@@ -2679,10 +2679,10 @@
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" t="s">
         <v>161</v>
-      </c>
-      <c r="C8" t="s">
-        <v>162</v>
       </c>
       <c r="D8" s="3">
         <v>2026</v>
@@ -2699,10 +2699,10 @@
         <v>20</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" t="s">
         <v>163</v>
-      </c>
-      <c r="C9" t="s">
-        <v>164</v>
       </c>
       <c r="D9" s="3">
         <v>2026</v>
@@ -2719,10 +2719,10 @@
         <v>20</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D10" s="3">
         <v>2026</v>
@@ -2739,10 +2739,10 @@
         <v>20</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D11" s="3">
         <v>2026</v>
@@ -2759,10 +2759,10 @@
         <v>20</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" s="3">
         <v>2026</v>
@@ -2779,10 +2779,10 @@
         <v>20</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" t="s">
         <v>168</v>
-      </c>
-      <c r="C13" t="s">
-        <v>169</v>
       </c>
       <c r="D13" s="3">
         <v>2026</v>
@@ -2799,10 +2799,10 @@
         <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D14" s="3">
         <v>2026</v>
@@ -2819,10 +2819,10 @@
         <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15" s="3">
         <v>2026</v>
@@ -2839,10 +2839,10 @@
         <v>20</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D16" s="3">
         <v>2026</v>
@@ -2859,10 +2859,10 @@
         <v>20</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D17" s="3">
         <v>2026</v>
@@ -2879,10 +2879,10 @@
         <v>20</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D18" s="3">
         <v>2026</v>
@@ -2899,10 +2899,10 @@
         <v>20</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D19" s="3">
         <v>2026</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>449</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>451</v>
       </c>
       <c r="C20" t="s">
         <v>41</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C21" t="s">
         <v>41</v>
@@ -2956,13 +2956,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C22" t="s">
         <v>453</v>
-      </c>
-      <c r="C22" t="s">
-        <v>454</v>
       </c>
       <c r="D22" s="3">
         <v>2026</v>
@@ -2976,13 +2976,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C23" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D23" s="3">
         <v>2026</v>
@@ -2996,13 +2996,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C24" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D24" s="3">
         <v>2026</v>
@@ -3016,13 +3016,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D25" s="3">
         <v>2026</v>
@@ -3036,13 +3036,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C26" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D26" s="3">
         <v>2026</v>
@@ -3056,13 +3056,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C27" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D27" s="3">
         <v>2026</v>
@@ -3076,13 +3076,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C28" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D28" s="3">
         <v>2026</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C29" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D29" s="3">
         <v>2026</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C30" t="s">
         <v>460</v>
-      </c>
-      <c r="C30" t="s">
-        <v>461</v>
       </c>
       <c r="D30" s="3">
         <v>2026</v>
@@ -3137,13 +3137,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B31" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="C31" t="s">
         <v>659</v>
-      </c>
-      <c r="C31" t="s">
-        <v>660</v>
       </c>
       <c r="D31" s="3">
         <v>2026</v>
@@ -3157,13 +3157,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D32" s="3">
         <v>2026</v>
@@ -3177,13 +3177,13 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C33" t="s">
         <v>463</v>
-      </c>
-      <c r="C33" t="s">
-        <v>464</v>
       </c>
       <c r="D33" s="3">
         <v>2026</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C34" t="s">
         <v>22</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C35" t="s">
         <v>22</v>
@@ -3237,13 +3237,13 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C36" t="s">
         <v>472</v>
-      </c>
-      <c r="C36" t="s">
-        <v>473</v>
       </c>
       <c r="D36" s="3">
         <v>2026</v>
@@ -3257,13 +3257,13 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C37" t="s">
         <v>474</v>
-      </c>
-      <c r="C37" t="s">
-        <v>475</v>
       </c>
       <c r="D37" s="3">
         <v>2026</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D38" s="3">
         <v>2026</v>
@@ -3297,13 +3297,13 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C39" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D39" s="3">
         <v>2026</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C40" t="s">
         <v>478</v>
-      </c>
-      <c r="C40" t="s">
-        <v>479</v>
       </c>
       <c r="D40" s="3">
         <v>2026</v>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D41" s="3">
         <v>2026</v>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C42" t="s">
         <v>481</v>
-      </c>
-      <c r="C42" t="s">
-        <v>482</v>
       </c>
       <c r="D42" s="3">
         <v>2026</v>
@@ -3380,7 +3380,7 @@
         <v>28</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -3400,10 +3400,10 @@
         <v>28</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D44" s="3">
         <v>2026</v>
@@ -3420,10 +3420,10 @@
         <v>28</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C45" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D45" s="3">
         <v>2026</v>
@@ -3440,10 +3440,10 @@
         <v>28</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C46" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D46" s="3">
         <v>2026</v>
@@ -3484,7 +3484,7 @@
         <v>29</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D48" s="3">
         <v>2026</v>
@@ -3502,10 +3502,10 @@
         <v>28</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D49" s="3">
         <v>2025</v>
@@ -3523,10 +3523,10 @@
         <v>28</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D50" s="3">
         <v>2025</v>
@@ -3568,7 +3568,7 @@
         <v>31</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D52" s="3">
         <v>2026</v>
@@ -3586,10 +3586,10 @@
         <v>28</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D53" s="3">
         <v>2026</v>
@@ -3607,7 +3607,7 @@
         <v>28</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C54" t="s">
         <v>26</v>
@@ -3628,10 +3628,10 @@
         <v>28</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D55" s="3">
         <v>2026</v>
@@ -3649,7 +3649,7 @@
         <v>28</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C56" t="s">
         <v>41</v>
@@ -3673,7 +3673,7 @@
         <v>33</v>
       </c>
       <c r="C57" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D57" s="3">
         <v>2026</v>
@@ -3691,10 +3691,10 @@
         <v>28</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D58" s="3">
         <v>2026</v>
@@ -3712,10 +3712,10 @@
         <v>28</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C59" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D59" s="3">
         <v>2025</v>
@@ -3733,10 +3733,10 @@
         <v>28</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C60" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D60" s="3">
         <v>2026</v>
@@ -3754,10 +3754,10 @@
         <v>28</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D61" s="3">
         <v>2026</v>
@@ -3775,7 +3775,7 @@
         <v>28</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -3796,10 +3796,10 @@
         <v>28</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D63" s="3">
         <v>2027</v>
@@ -3817,10 +3817,10 @@
         <v>48</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D64" s="3">
         <v>2027</v>
@@ -3838,10 +3838,10 @@
         <v>48</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>49</v>
+        <v>665</v>
       </c>
       <c r="C65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D65" s="3">
         <v>2027</v>
@@ -3853,7 +3853,7 @@
         <v>174990</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O65" s="1"/>
     </row>
@@ -3862,7 +3862,7 @@
         <v>48</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C66" s="12">
         <v>11</v>
@@ -3898,7 +3898,7 @@
         <v>149990</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O67" s="1"/>
     </row>
@@ -3910,7 +3910,7 @@
         <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D68" s="3">
         <v>2027</v>
@@ -3922,7 +3922,7 @@
         <v>126990</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O68" s="1"/>
     </row>
@@ -3946,7 +3946,7 @@
         <v>146990</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O69" s="1"/>
     </row>
@@ -3955,10 +3955,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C70" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D70" s="3">
         <v>2027</v>
@@ -3970,7 +3970,7 @@
         <v>147990</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O70" s="1"/>
     </row>
@@ -3979,10 +3979,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C71" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D71" s="3">
         <v>2027</v>
@@ -3994,7 +3994,7 @@
         <v>184990</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O71" s="1"/>
     </row>
@@ -4003,10 +4003,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" t="s">
         <v>59</v>
-      </c>
-      <c r="C72" t="s">
-        <v>60</v>
       </c>
       <c r="D72" s="3">
         <v>2027</v>
@@ -4018,7 +4018,7 @@
         <v>189990</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O72" s="1"/>
     </row>
@@ -4027,10 +4027,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C73" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D73" s="3">
         <v>2027</v>
@@ -4042,7 +4042,7 @@
         <v>181990</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O73" s="1"/>
     </row>
@@ -4051,7 +4051,7 @@
         <v>14</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C74" t="s">
         <v>19</v>
@@ -4066,7 +4066,7 @@
         <v>189990</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O74" s="1"/>
     </row>
@@ -4075,10 +4075,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C75" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D75" s="3">
         <v>2027</v>
@@ -4090,7 +4090,7 @@
         <v>181990</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O75" s="1"/>
     </row>
@@ -4099,7 +4099,7 @@
         <v>37</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C76" t="s">
         <v>41</v>
@@ -4123,10 +4123,10 @@
         <v>37</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C77" t="s">
         <v>329</v>
-      </c>
-      <c r="C77" t="s">
-        <v>330</v>
       </c>
       <c r="D77" s="3">
         <v>2026</v>
@@ -4195,10 +4195,10 @@
         <v>37</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D80" s="3">
         <v>2026</v>
@@ -4210,7 +4210,7 @@
         <v>101790</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -4218,10 +4218,10 @@
         <v>37</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D81" s="3">
         <v>2026</v>
@@ -4233,7 +4233,7 @@
         <v>109990</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -4241,10 +4241,10 @@
         <v>37</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C82" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D82" s="3">
         <v>2026</v>
@@ -4256,7 +4256,7 @@
         <v>114990</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -4264,10 +4264,10 @@
         <v>37</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D83" s="3">
         <v>2026</v>
@@ -4279,7 +4279,7 @@
         <v>120990</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -4287,10 +4287,10 @@
         <v>37</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C84" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D84" s="3">
         <v>2026</v>
@@ -4302,7 +4302,7 @@
         <v>126190</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -4310,10 +4310,10 @@
         <v>37</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D85" s="3">
         <v>2026</v>
@@ -4325,7 +4325,7 @@
         <v>132390</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -4333,10 +4333,10 @@
         <v>37</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C86" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D86" s="3">
         <v>2026</v>
@@ -4348,7 +4348,7 @@
         <v>133390</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -4356,10 +4356,10 @@
         <v>37</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C87" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D87" s="3">
         <v>2026</v>
@@ -4371,7 +4371,7 @@
         <v>108990</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -4379,10 +4379,10 @@
         <v>37</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C88" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D88" s="3">
         <v>2026</v>
@@ -4394,7 +4394,7 @@
         <v>115990</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -4402,10 +4402,10 @@
         <v>37</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C89" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D89" s="3">
         <v>2026</v>
@@ -4417,7 +4417,7 @@
         <v>121190</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -4425,10 +4425,10 @@
         <v>37</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C90" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D90" s="3">
         <v>2026</v>
@@ -4440,7 +4440,7 @@
         <v>126390</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -4448,10 +4448,10 @@
         <v>37</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C91" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D91" s="3">
         <v>2026</v>
@@ -4463,7 +4463,7 @@
         <v>132390</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -4471,10 +4471,10 @@
         <v>37</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C92" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D92" s="3">
         <v>2026</v>
@@ -4486,7 +4486,7 @@
         <v>139390</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -4494,10 +4494,10 @@
         <v>37</v>
       </c>
       <c r="B93" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C93" t="s">
         <v>86</v>
-      </c>
-      <c r="C93" t="s">
-        <v>87</v>
       </c>
       <c r="D93" s="3">
         <v>2026</v>
@@ -4509,7 +4509,7 @@
         <v>315000</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -4517,10 +4517,10 @@
         <v>37</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C94" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D94" s="3">
         <v>2026</v>
@@ -4532,7 +4532,7 @@
         <v>119990</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -4540,10 +4540,10 @@
         <v>37</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C95" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D95" s="3">
         <v>2026</v>
@@ -4555,7 +4555,7 @@
         <v>145490</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -4563,10 +4563,10 @@
         <v>37</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C96" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D96" s="3">
         <v>2026</v>
@@ -4578,7 +4578,7 @@
         <v>160790</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
@@ -4586,10 +4586,10 @@
         <v>37</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C97" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D97" s="3">
         <v>2026</v>
@@ -4601,7 +4601,7 @@
         <v>177990</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
@@ -4609,10 +4609,10 @@
         <v>37</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C98" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D98" s="3">
         <v>2026</v>
@@ -4624,7 +4624,7 @@
         <v>178990</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
@@ -4632,10 +4632,10 @@
         <v>37</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C99" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D99" s="3">
         <v>2026</v>
@@ -4647,7 +4647,7 @@
         <v>291190</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O99" s="1"/>
     </row>
@@ -4656,10 +4656,10 @@
         <v>37</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C100" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D100" s="3">
         <v>2026</v>
@@ -4671,7 +4671,7 @@
         <v>291190</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O100" s="1"/>
     </row>
@@ -4680,10 +4680,10 @@
         <v>37</v>
       </c>
       <c r="B101" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C101" t="s">
         <v>331</v>
-      </c>
-      <c r="C101" t="s">
-        <v>332</v>
       </c>
       <c r="D101" s="3">
         <v>2027</v>
@@ -4695,7 +4695,7 @@
         <v>422590</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
@@ -4703,10 +4703,10 @@
         <v>37</v>
       </c>
       <c r="B102" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C102" t="s">
         <v>341</v>
-      </c>
-      <c r="C102" t="s">
-        <v>342</v>
       </c>
       <c r="D102" s="3">
         <v>2027</v>
@@ -4718,7 +4718,7 @@
         <v>131990</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4726,10 +4726,10 @@
         <v>37</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C103" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D103" s="3">
         <v>2027</v>
@@ -4741,7 +4741,7 @@
         <v>137690</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
@@ -4749,10 +4749,10 @@
         <v>37</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C104" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D104" s="3">
         <v>2027</v>
@@ -4764,7 +4764,7 @@
         <v>154990</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
@@ -4772,10 +4772,10 @@
         <v>37</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C105" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D105" s="3">
         <v>2027</v>
@@ -4787,7 +4787,7 @@
         <v>162990</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
@@ -4795,10 +4795,10 @@
         <v>37</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C106" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D106" s="3">
         <v>2027</v>
@@ -4810,7 +4810,7 @@
         <v>167990</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4818,10 +4818,10 @@
         <v>37</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C107" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D107" s="3">
         <v>2027</v>
@@ -4833,7 +4833,7 @@
         <v>129990</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
@@ -4841,10 +4841,10 @@
         <v>37</v>
       </c>
       <c r="B108" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C108" t="s">
         <v>339</v>
-      </c>
-      <c r="C108" t="s">
-        <v>340</v>
       </c>
       <c r="D108" s="3">
         <v>2027</v>
@@ -4856,7 +4856,7 @@
         <v>135990</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
@@ -4864,10 +4864,10 @@
         <v>37</v>
       </c>
       <c r="B109" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C109" t="s">
         <v>335</v>
-      </c>
-      <c r="C109" t="s">
-        <v>336</v>
       </c>
       <c r="D109" s="3">
         <v>2027</v>
@@ -4879,7 +4879,7 @@
         <v>119990</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
@@ -4887,10 +4887,10 @@
         <v>37</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C110" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D110" s="3">
         <v>2027</v>
@@ -4902,7 +4902,7 @@
         <v>138590</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
@@ -4910,10 +4910,10 @@
         <v>37</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C111" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D111" s="3">
         <v>2027</v>
@@ -4925,7 +4925,7 @@
         <v>153990</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
@@ -4933,10 +4933,10 @@
         <v>37</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C112" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D112" s="3">
         <v>2027</v>
@@ -4948,7 +4948,7 @@
         <v>165590</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
@@ -4956,10 +4956,10 @@
         <v>37</v>
       </c>
       <c r="B113" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C113" t="s">
         <v>353</v>
-      </c>
-      <c r="C113" t="s">
-        <v>354</v>
       </c>
       <c r="D113" s="3">
         <v>2026</v>
@@ -4971,7 +4971,7 @@
         <v>483990</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
@@ -4979,10 +4979,10 @@
         <v>37</v>
       </c>
       <c r="B114" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C114" t="s">
         <v>86</v>
-      </c>
-      <c r="C114" t="s">
-        <v>87</v>
       </c>
       <c r="D114" s="3">
         <v>2027</v>
@@ -4999,10 +4999,10 @@
         <v>37</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D115" s="3">
         <v>2027</v>
@@ -5019,10 +5019,10 @@
         <v>37</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C116" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D116" s="3">
         <v>2027</v>
@@ -5039,10 +5039,10 @@
         <v>37</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C117" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D117" s="3">
         <v>2027</v>
@@ -5054,7 +5054,7 @@
         <v>304590</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
@@ -5062,10 +5062,10 @@
         <v>37</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C118" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D118" s="3">
         <v>2027</v>
@@ -5077,7 +5077,7 @@
         <v>285890</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -5085,10 +5085,10 @@
         <v>37</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C119" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D119" s="3">
         <v>2027</v>
@@ -5102,13 +5102,13 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
+        <v>89</v>
+      </c>
+      <c r="B120" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B120" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="C120" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D120" s="3">
         <v>2026</v>
@@ -5120,18 +5120,18 @@
         <v>87450</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
+        <v>89</v>
+      </c>
+      <c r="B121" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B121" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="C121" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D121" s="3">
         <v>2026</v>
@@ -5143,18 +5143,18 @@
         <v>93590</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
+        <v>89</v>
+      </c>
+      <c r="B122" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B122" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="C122" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D122" s="3">
         <v>2026</v>
@@ -5166,18 +5166,18 @@
         <v>97590</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
+        <v>89</v>
+      </c>
+      <c r="B123" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B123" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="C123" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D123" s="3">
         <v>2026</v>
@@ -5189,18 +5189,18 @@
         <v>100590</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
+        <v>89</v>
+      </c>
+      <c r="B124" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B124" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="C124" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D124" s="3">
         <v>2026</v>
@@ -5212,18 +5212,18 @@
         <v>112590</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C125" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D125" s="3">
         <v>2026</v>
@@ -5235,18 +5235,18 @@
         <v>119990</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C126" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D126" s="3">
         <v>2026</v>
@@ -5258,18 +5258,18 @@
         <v>123790</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C127" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D127" s="3">
         <v>2026</v>
@@ -5281,18 +5281,18 @@
         <v>131790</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C128" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D128" s="3">
         <v>2026</v>
@@ -5304,18 +5304,18 @@
         <v>134790</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B129" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C129" t="s">
         <v>209</v>
-      </c>
-      <c r="C129" t="s">
-        <v>210</v>
       </c>
       <c r="D129" s="3">
         <v>2026</v>
@@ -5327,18 +5327,18 @@
         <v>97690</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C130" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D130" s="3">
         <v>2026</v>
@@ -5350,18 +5350,18 @@
         <v>112690</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C131" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D131" s="3">
         <v>2026</v>
@@ -5373,18 +5373,18 @@
         <v>117990</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C132" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D132" s="3">
         <v>2026</v>
@@ -5396,18 +5396,18 @@
         <v>119690</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>92</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B133" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="C133" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D133" s="3">
         <v>2026</v>
@@ -5419,18 +5419,18 @@
         <v>96980</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>92</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B134" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="C134" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D134" s="3">
         <v>2026</v>
@@ -5442,18 +5442,18 @@
         <v>97990</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>92</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B135" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="C135" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D135" s="3">
         <v>2026</v>
@@ -5465,18 +5465,18 @@
         <v>109980</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>92</v>
+      </c>
+      <c r="B136" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B136" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="C136" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D136" s="3">
         <v>2026</v>
@@ -5488,18 +5488,18 @@
         <v>103990</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
+        <v>92</v>
+      </c>
+      <c r="B137" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B137" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="C137" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D137" s="3">
         <v>2026</v>
@@ -5511,18 +5511,18 @@
         <v>112980</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C138" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D138" s="3">
         <v>2026</v>
@@ -5534,18 +5534,18 @@
         <v>109990</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B139" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C139" t="s">
         <v>375</v>
-      </c>
-      <c r="C139" t="s">
-        <v>376</v>
       </c>
       <c r="D139" s="3">
         <v>2026</v>
@@ -5557,18 +5557,18 @@
         <v>114990</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C140" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D140" s="3">
         <v>2026</v>
@@ -5580,18 +5580,18 @@
         <v>121980</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C141" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D141" s="3">
         <v>2026</v>
@@ -5603,18 +5603,18 @@
         <v>127980</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C142" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D142" s="3">
         <v>2026</v>
@@ -5626,18 +5626,18 @@
         <v>119990</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C143" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D143" s="3">
         <v>2026</v>
@@ -5649,18 +5649,18 @@
         <v>167490</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C144" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D144" s="3">
         <v>2026</v>
@@ -5672,18 +5672,18 @@
         <v>173490</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C145" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D145" s="3">
         <v>2026</v>
@@ -5695,18 +5695,18 @@
         <v>177990</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C146" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D146" s="3">
         <v>2026</v>
@@ -5718,18 +5718,18 @@
         <v>184980</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B147" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C147" t="s">
         <v>96</v>
-      </c>
-      <c r="C147" t="s">
-        <v>97</v>
       </c>
       <c r="D147" s="3">
         <v>2026</v>
@@ -5741,18 +5741,18 @@
         <v>83490</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C148" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D148" s="3">
         <v>2026</v>
@@ -5764,18 +5764,18 @@
         <v>85990</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C149" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D149" s="3">
         <v>2026</v>
@@ -5787,18 +5787,18 @@
         <v>103990</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C150" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D150" s="3">
         <v>2026</v>
@@ -5810,18 +5810,18 @@
         <v>115990</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C151" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D151" s="3">
         <v>2026</v>
@@ -5833,18 +5833,18 @@
         <v>119990</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C152" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D152" s="3">
         <v>2026</v>
@@ -5856,18 +5856,18 @@
         <v>136990</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C153" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D153" s="3">
         <v>2026</v>
@@ -5879,18 +5879,18 @@
         <v>151490</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C154" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D154" s="3">
         <v>2026</v>
@@ -5902,18 +5902,18 @@
         <v>162490</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C155" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D155" s="3">
         <v>2026</v>
@@ -5925,18 +5925,18 @@
         <v>153990</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C156" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D156" s="3">
         <v>2026</v>
@@ -5948,18 +5948,18 @@
         <v>153990</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C157" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D157" s="3">
         <v>2026</v>
@@ -5971,18 +5971,18 @@
         <v>142490</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C158" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D158" s="3">
         <v>2026</v>
@@ -5994,18 +5994,18 @@
         <v>136490</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C159" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D159" s="3">
         <v>2026</v>
@@ -6017,18 +6017,18 @@
         <v>133490</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C160" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D160" s="3">
         <v>2026</v>
@@ -6040,18 +6040,18 @@
         <v>123990</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C161" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D161" s="3">
         <v>2026</v>
@@ -6063,18 +6063,18 @@
         <v>116990</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C162" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D162" s="3">
         <v>2026</v>
@@ -6086,18 +6086,18 @@
         <v>167490</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C163" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D163" s="3">
         <v>2026</v>
@@ -6109,18 +6109,18 @@
         <v>177490</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C164" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D164" s="3">
         <v>2026</v>
@@ -6132,18 +6132,18 @@
         <v>197490</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C165" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D165" s="3">
         <v>2026</v>
@@ -6155,18 +6155,18 @@
         <v>206490</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C166" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D166" s="3">
         <v>2026</v>
@@ -6178,18 +6178,18 @@
         <v>220490</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C167" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D167" s="3">
         <v>2026</v>
@@ -6201,18 +6201,18 @@
         <v>238490</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B168" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C168" t="s">
         <v>396</v>
-      </c>
-      <c r="C168" t="s">
-        <v>397</v>
       </c>
       <c r="D168" s="3">
         <v>2026</v>
@@ -6224,18 +6224,18 @@
         <v>238490</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C169" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D169" s="3">
         <v>2026</v>
@@ -6247,18 +6247,18 @@
         <v>268490</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C170" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D170" s="3">
         <v>2026</v>
@@ -6270,18 +6270,18 @@
         <v>291990</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B171" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C171" t="s">
         <v>398</v>
-      </c>
-      <c r="C171" t="s">
-        <v>399</v>
       </c>
       <c r="D171" s="3">
         <v>2022</v>
@@ -6298,13 +6298,13 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
+        <v>277</v>
+      </c>
+      <c r="B172" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="C172" t="s">
         <v>279</v>
-      </c>
-      <c r="C172" t="s">
-        <v>280</v>
       </c>
       <c r="D172" s="3">
         <v>2026</v>
@@ -6318,13 +6318,13 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C173" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D173" s="3">
         <v>2026</v>
@@ -6338,13 +6338,13 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B174" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C174" t="s">
         <v>283</v>
-      </c>
-      <c r="C174" t="s">
-        <v>284</v>
       </c>
       <c r="D174" s="3">
         <v>2026</v>
@@ -6358,13 +6358,13 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C175" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D175" s="3">
         <v>2026</v>
@@ -6378,13 +6378,13 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B176" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C176" t="s">
         <v>286</v>
-      </c>
-      <c r="C176" t="s">
-        <v>287</v>
       </c>
       <c r="D176" s="3">
         <v>2025</v>
@@ -6398,13 +6398,13 @@
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B177" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C177" t="s">
         <v>288</v>
-      </c>
-      <c r="C177" t="s">
-        <v>289</v>
       </c>
       <c r="D177" s="3">
         <v>2026</v>
@@ -6418,13 +6418,13 @@
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C178" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D178" s="3">
         <v>2026</v>
@@ -6438,13 +6438,13 @@
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C179" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D179" s="3">
         <v>2026</v>
@@ -6458,13 +6458,13 @@
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B180" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C180" t="s">
         <v>292</v>
-      </c>
-      <c r="C180" t="s">
-        <v>293</v>
       </c>
       <c r="D180" s="3">
         <v>2026</v>
@@ -6478,13 +6478,13 @@
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C181" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D181" s="3">
         <v>2026</v>
@@ -6498,13 +6498,13 @@
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C182" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D182" s="3">
         <v>2026</v>
@@ -6518,13 +6518,13 @@
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C183" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D183" s="3">
         <v>2026</v>
@@ -6538,13 +6538,13 @@
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C184" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D184" s="3">
         <v>2027</v>
@@ -6558,13 +6558,13 @@
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C185" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D185" s="3">
         <v>2026</v>
@@ -6578,13 +6578,13 @@
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C186" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D186" s="3">
         <v>2026</v>
@@ -6616,7 +6616,7 @@
         <v>159990</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O187" s="1"/>
     </row>
@@ -6640,7 +6640,7 @@
         <v>139990</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O188" s="1"/>
     </row>
@@ -6649,7 +6649,7 @@
         <v>23</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C189" t="s">
         <v>25</v>
@@ -6664,7 +6664,7 @@
         <v>209990</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O189" s="1"/>
     </row>
@@ -6673,7 +6673,7 @@
         <v>23</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C190" t="s">
         <v>26</v>
@@ -6688,7 +6688,7 @@
         <v>191990</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O190" s="1"/>
     </row>
@@ -6745,7 +6745,7 @@
         <v>23</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C193" t="s">
         <v>25</v>
@@ -6769,7 +6769,7 @@
         <v>23</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C194" t="s">
         <v>26</v>
@@ -6793,7 +6793,7 @@
         <v>23</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C195" t="s">
         <v>25</v>
@@ -6817,10 +6817,10 @@
         <v>23</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C196" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D196" s="3">
         <v>2026</v>
@@ -6841,7 +6841,7 @@
         <v>23</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C197" t="s">
         <v>25</v>
@@ -6865,10 +6865,10 @@
         <v>23</v>
       </c>
       <c r="B198" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C198" t="s">
         <v>153</v>
-      </c>
-      <c r="C198" t="s">
-        <v>154</v>
       </c>
       <c r="D198" s="3">
         <v>2026</v>
@@ -6937,7 +6937,7 @@
         <v>34</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C201" t="s">
         <v>19</v>
@@ -6961,7 +6961,7 @@
         <v>34</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C202" t="s">
         <v>36</v>
@@ -6985,7 +6985,7 @@
         <v>34</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C203" t="s">
         <v>19</v>
@@ -7000,7 +7000,7 @@
         <v>189990</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O203" s="1"/>
     </row>
@@ -7009,7 +7009,7 @@
         <v>34</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C204" t="s">
         <v>36</v>
@@ -7024,7 +7024,7 @@
         <v>209990</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O204" s="1"/>
     </row>
@@ -7033,10 +7033,10 @@
         <v>34</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C205" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D205" s="3">
         <v>2027</v>
@@ -7048,19 +7048,19 @@
         <v>234990</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O205" s="1"/>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C206" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D206" s="3">
         <v>2026</v>
@@ -7075,13 +7075,13 @@
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C207" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D207" s="3">
         <v>2026</v>
@@ -7096,13 +7096,13 @@
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B208" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C208" t="s">
         <v>406</v>
-      </c>
-      <c r="C208" t="s">
-        <v>407</v>
       </c>
       <c r="D208" s="3">
         <v>2026</v>
@@ -7117,13 +7117,13 @@
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B209" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C209" t="s">
         <v>408</v>
-      </c>
-      <c r="C209" t="s">
-        <v>409</v>
       </c>
       <c r="D209" s="3">
         <v>2026</v>
@@ -7138,13 +7138,13 @@
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C210" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D210" s="3">
         <v>2026</v>
@@ -7159,13 +7159,13 @@
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C211" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D211" s="3">
         <v>2026</v>
@@ -7180,13 +7180,13 @@
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
+        <v>100</v>
+      </c>
+      <c r="B212" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B212" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="C212" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D212" s="3">
         <v>2026</v>
@@ -7201,13 +7201,13 @@
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
+        <v>100</v>
+      </c>
+      <c r="B213" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B213" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="C213" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D213" s="3">
         <v>2026</v>
@@ -7222,13 +7222,13 @@
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
+        <v>100</v>
+      </c>
+      <c r="B214" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B214" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="C214" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D214" s="3">
         <v>2026</v>
@@ -7243,13 +7243,13 @@
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
+        <v>100</v>
+      </c>
+      <c r="B215" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="C215" t="s">
         <v>102</v>
-      </c>
-      <c r="C215" t="s">
-        <v>103</v>
       </c>
       <c r="D215" s="3">
         <v>2026</v>
@@ -7263,13 +7263,13 @@
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
+        <v>100</v>
+      </c>
+      <c r="B216" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B216" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="C216" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D216" s="3">
         <v>2026</v>
@@ -7283,13 +7283,13 @@
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C217" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D217" s="3">
         <v>2026</v>
@@ -7303,13 +7303,13 @@
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C218" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D218" s="3">
         <v>2026</v>
@@ -7323,13 +7323,13 @@
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C219" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D219" s="3">
         <v>2026</v>
@@ -7343,13 +7343,13 @@
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B220" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C220" t="s">
         <v>363</v>
-      </c>
-      <c r="C220" t="s">
-        <v>364</v>
       </c>
       <c r="D220" s="3">
         <v>2026</v>
@@ -7363,13 +7363,13 @@
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C221" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D221" s="3">
         <v>2026</v>
@@ -7383,13 +7383,13 @@
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C222" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D222" s="3">
         <v>2026</v>
@@ -7403,13 +7403,13 @@
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C223" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D223" s="3">
         <v>2026</v>
@@ -7423,13 +7423,13 @@
     </row>
     <row r="224" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C224" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D224" s="3">
         <v>2026</v>
@@ -7443,13 +7443,13 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
+        <v>104</v>
+      </c>
+      <c r="B225" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B225" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="C225" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D225" s="3">
         <v>2026</v>
@@ -7463,13 +7463,13 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
+        <v>104</v>
+      </c>
+      <c r="B226" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B226" s="4" t="s">
+      <c r="C226" t="s">
         <v>106</v>
-      </c>
-      <c r="C226" t="s">
-        <v>107</v>
       </c>
       <c r="D226" s="3">
         <v>2026</v>
@@ -7483,13 +7483,13 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
+        <v>104</v>
+      </c>
+      <c r="B227" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B227" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="C227" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D227" s="3">
         <v>2026</v>
@@ -7503,13 +7503,13 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
+        <v>104</v>
+      </c>
+      <c r="B228" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B228" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="C228" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D228" s="3">
         <v>2026</v>
@@ -7523,13 +7523,13 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C229" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D229" s="3">
         <v>2026</v>
@@ -7543,13 +7543,13 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C230" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D230" s="3">
         <v>2026</v>
@@ -7563,13 +7563,13 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C231" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D231" s="3">
         <v>2026</v>
@@ -7583,13 +7583,13 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C232" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D232" s="3">
         <v>2026</v>
@@ -7603,13 +7603,13 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C233" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D233" s="3">
         <v>2026</v>
@@ -7623,13 +7623,13 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C234" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D234" s="3">
         <v>2026</v>
@@ -7643,13 +7643,13 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C235" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D235" s="3">
         <v>2026</v>
@@ -7663,13 +7663,13 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C236" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D236" s="3">
         <v>2026</v>
@@ -7683,13 +7683,13 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C237" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D237" s="3">
         <v>2026</v>
@@ -7703,13 +7703,13 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C238" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D238" s="3">
         <v>2026</v>
@@ -7723,13 +7723,13 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
+        <v>109</v>
+      </c>
+      <c r="B239" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B239" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="C239" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D239" s="3">
         <v>2026</v>
@@ -7743,13 +7743,13 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
+        <v>109</v>
+      </c>
+      <c r="B240" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B240" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="C240" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D240" s="3">
         <v>2026</v>
@@ -7763,13 +7763,13 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
+        <v>109</v>
+      </c>
+      <c r="B241" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B241" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="C241" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D241" s="3">
         <v>2026</v>
@@ -7783,13 +7783,13 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
+        <v>109</v>
+      </c>
+      <c r="B242" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B242" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="C242" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D242" s="3">
         <v>2026</v>
@@ -7803,13 +7803,13 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B243" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C243" t="s">
         <v>427</v>
-      </c>
-      <c r="C243" t="s">
-        <v>428</v>
       </c>
       <c r="D243" s="3">
         <v>2026</v>
@@ -7823,13 +7823,13 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B244" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C244" t="s">
         <v>422</v>
-      </c>
-      <c r="C244" t="s">
-        <v>423</v>
       </c>
       <c r="D244" s="3">
         <v>2026</v>
@@ -7843,13 +7843,13 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C245" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D245" s="3">
         <v>2026</v>
@@ -7863,13 +7863,13 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C246" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D246" s="3">
         <v>2026</v>
@@ -7883,13 +7883,13 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C247" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D247" s="3">
         <v>2026</v>
@@ -7903,13 +7903,13 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C248" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D248" s="3">
         <v>2026</v>
@@ -7923,13 +7923,13 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C249" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D249" s="3">
         <v>2026</v>
@@ -7943,13 +7943,13 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C250" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D250" s="3">
         <v>2026</v>
@@ -7963,13 +7963,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C251" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D251" s="3">
         <v>2026</v>
@@ -7983,13 +7983,13 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C252" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D252" s="3">
         <v>2026</v>
@@ -8003,13 +8003,13 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C253" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D253" s="3">
         <v>2026</v>
@@ -8023,13 +8023,13 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B254" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C254" t="s">
         <v>416</v>
-      </c>
-      <c r="C254" t="s">
-        <v>417</v>
       </c>
       <c r="D254" s="3">
         <v>2026</v>
@@ -8043,13 +8043,13 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C255" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D255" s="3">
         <v>2025</v>
@@ -8063,13 +8063,13 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
+        <v>641</v>
+      </c>
+      <c r="B256" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="B256" s="4" t="s">
+      <c r="C256" t="s">
         <v>643</v>
-      </c>
-      <c r="C256" t="s">
-        <v>644</v>
       </c>
       <c r="D256" s="3">
         <v>2025</v>
@@ -8083,13 +8083,13 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
+        <v>641</v>
+      </c>
+      <c r="B257" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="B257" s="4" t="s">
-        <v>643</v>
-      </c>
       <c r="C257" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D257" s="3">
         <v>2025</v>
@@ -8103,13 +8103,13 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C258" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D258" s="3">
         <v>2025</v>
@@ -8123,13 +8123,13 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C259" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D259" s="3">
         <v>2025</v>
@@ -8143,13 +8143,13 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C260" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D260" s="3">
         <v>2026</v>
@@ -8163,13 +8163,13 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C261" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D261" s="3">
         <v>2026</v>
@@ -8183,13 +8183,13 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C262" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D262" s="3">
         <v>2026</v>
@@ -8203,13 +8203,13 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C263" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D263" s="3">
         <v>2026</v>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C264" t="s">
         <v>25</v>
@@ -8243,10 +8243,10 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C265" t="s">
         <v>44</v>
@@ -8263,13 +8263,13 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C266" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D266" s="3">
         <v>2027</v>
@@ -8283,13 +8283,13 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
+        <v>557</v>
+      </c>
+      <c r="B267" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="B267" s="4" t="s">
+      <c r="C267" t="s">
         <v>559</v>
-      </c>
-      <c r="C267" t="s">
-        <v>560</v>
       </c>
       <c r="D267" s="3">
         <v>2024</v>
@@ -8303,13 +8303,13 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C268" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D268" s="3">
         <v>2024</v>
@@ -8323,13 +8323,13 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C269" s="11" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D269" s="3">
         <v>2024</v>
@@ -8343,13 +8343,13 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C270" s="11" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D270" s="3">
         <v>2024</v>
@@ -8363,13 +8363,13 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B271" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C271" t="s">
         <v>562</v>
-      </c>
-      <c r="C271" t="s">
-        <v>563</v>
       </c>
       <c r="D271" s="3">
         <v>2024</v>
@@ -8383,13 +8383,13 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D272" s="3">
         <v>2024</v>
@@ -8403,13 +8403,13 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C273" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D273" s="3">
         <v>2027</v>
@@ -8423,13 +8423,13 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C274" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D274" s="3">
         <v>2027</v>
@@ -8443,13 +8443,13 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C275" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D275" s="3">
         <v>2026</v>
@@ -8461,18 +8461,18 @@
         <v>175990</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C276" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D276" s="3">
         <v>2027</v>
@@ -8484,18 +8484,18 @@
         <v>158990</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C277" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D277" s="3">
         <v>2026</v>
@@ -8509,13 +8509,13 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
+        <v>113</v>
+      </c>
+      <c r="B278" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B278" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="C278" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D278" s="3">
         <v>2026</v>
@@ -8529,13 +8529,13 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
+        <v>113</v>
+      </c>
+      <c r="B279" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B279" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="C279" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D279" s="3">
         <v>2026</v>
@@ -8547,18 +8547,18 @@
         <v>255690</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
+        <v>113</v>
+      </c>
+      <c r="B280" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B280" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="C280" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D280" s="3">
         <v>2026</v>
@@ -8570,18 +8570,18 @@
         <v>283790</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
+        <v>113</v>
+      </c>
+      <c r="B281" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B281" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="C281" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D281" s="3">
         <v>2026</v>
@@ -8595,13 +8595,13 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
+        <v>113</v>
+      </c>
+      <c r="B282" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B282" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="C282" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D282" s="3">
         <v>2026</v>
@@ -8615,13 +8615,13 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C283" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D283" s="3">
         <v>2026</v>
@@ -8633,18 +8633,18 @@
         <v>174990</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B284" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C284" t="s">
         <v>116</v>
-      </c>
-      <c r="C284" t="s">
-        <v>117</v>
       </c>
       <c r="D284" s="3">
         <v>2026</v>
@@ -8656,18 +8656,18 @@
         <v>201490</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C285" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D285" s="3">
         <v>2026</v>
@@ -8679,18 +8679,18 @@
         <v>233990</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C286" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D286" s="3">
         <v>2026</v>
@@ -8702,18 +8702,18 @@
         <v>278990</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B287" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C287" t="s">
         <v>232</v>
-      </c>
-      <c r="C287" t="s">
-        <v>233</v>
       </c>
       <c r="D287" s="3">
         <v>2026</v>
@@ -8727,13 +8727,13 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C288" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D288" s="3">
         <v>2026</v>
@@ -8747,13 +8747,13 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
+        <v>77</v>
+      </c>
+      <c r="B289" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B289" s="4" t="s">
+      <c r="C289" t="s">
         <v>79</v>
-      </c>
-      <c r="C289" t="s">
-        <v>80</v>
       </c>
       <c r="D289" s="3">
         <v>2026</v>
@@ -8767,10 +8767,10 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
+        <v>77</v>
+      </c>
+      <c r="B290" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="B290" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="C290" t="s">
         <v>26</v>
@@ -8787,13 +8787,13 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C291" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D291" s="3">
         <v>2026</v>
@@ -8807,10 +8807,10 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C292" t="s">
         <v>26</v>
@@ -8827,13 +8827,13 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C293" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D293" s="3">
         <v>2026</v>
@@ -8847,10 +8847,10 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C294" t="s">
         <v>26</v>
@@ -8867,13 +8867,13 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
+        <v>589</v>
+      </c>
+      <c r="B295" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="B295" s="4" t="s">
-        <v>591</v>
-      </c>
       <c r="C295" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D295" s="3">
         <v>2026</v>
@@ -8887,13 +8887,13 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B296" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="C296" s="11" t="s">
         <v>592</v>
-      </c>
-      <c r="C296" s="11" t="s">
-        <v>593</v>
       </c>
       <c r="D296" s="3">
         <v>2026</v>
@@ -8907,13 +8907,13 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C297" s="11" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D297" s="3">
         <v>2026</v>
@@ -8927,13 +8927,13 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B298" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="C298" s="11" t="s">
         <v>595</v>
-      </c>
-      <c r="C298" s="11" t="s">
-        <v>596</v>
       </c>
       <c r="D298" s="3">
         <v>2026</v>
@@ -8947,13 +8947,13 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B299" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="C299" s="11" t="s">
         <v>597</v>
-      </c>
-      <c r="C299" s="11" t="s">
-        <v>598</v>
       </c>
       <c r="D299" s="3">
         <v>2025</v>
@@ -8967,13 +8967,13 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B300" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C300" s="11" t="s">
         <v>599</v>
-      </c>
-      <c r="C300" s="11" t="s">
-        <v>600</v>
       </c>
       <c r="D300" s="3">
         <v>2026</v>
@@ -8987,13 +8987,13 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C301" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D301" s="3">
         <v>2026</v>
@@ -9007,13 +9007,13 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D302" s="3">
         <v>2027</v>
@@ -9027,13 +9027,13 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C303" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D303" s="3">
         <v>2027</v>
@@ -9047,13 +9047,13 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C304" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D304" s="3">
         <v>2027</v>
@@ -9067,13 +9067,13 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B305" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="C305" t="s">
         <v>619</v>
-      </c>
-      <c r="C305" t="s">
-        <v>620</v>
       </c>
       <c r="D305" s="3">
         <v>2026</v>
@@ -9087,13 +9087,13 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C306" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D306" s="3">
         <v>2026</v>
@@ -9107,13 +9107,13 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C307" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D307" s="3">
         <v>2026</v>
@@ -9127,13 +9127,13 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C308" s="12" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D308" s="3">
         <v>2026</v>
@@ -9147,13 +9147,13 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B309" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="C309" s="12" t="s">
         <v>619</v>
-      </c>
-      <c r="C309" s="12" t="s">
-        <v>620</v>
       </c>
       <c r="D309" s="3">
         <v>2026</v>
@@ -9167,13 +9167,13 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C310" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D310" s="3">
         <v>2026</v>
@@ -9187,13 +9187,13 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D311" s="3">
         <v>2026</v>
@@ -9207,13 +9207,13 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
+        <v>616</v>
+      </c>
+      <c r="B312" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="B312" s="4" t="s">
-        <v>618</v>
-      </c>
       <c r="C312" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D312" s="3">
         <v>2026</v>
@@ -9227,13 +9227,13 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
+        <v>616</v>
+      </c>
+      <c r="B313" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="B313" s="4" t="s">
-        <v>618</v>
-      </c>
       <c r="C313" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D313" s="3">
         <v>2026</v>
@@ -9247,13 +9247,13 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C314" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D314" s="3">
         <v>2026</v>
@@ -9267,13 +9267,13 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C315" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D315" s="3">
         <v>2026</v>
@@ -9287,13 +9287,13 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C316" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D316" s="3">
         <v>2026</v>
@@ -9307,13 +9307,13 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B317" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C317" t="s">
         <v>402</v>
-      </c>
-      <c r="C317" t="s">
-        <v>403</v>
       </c>
       <c r="D317" s="3">
         <v>2026</v>
@@ -9327,13 +9327,13 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
+        <v>399</v>
+      </c>
+      <c r="B318" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="B318" s="4" t="s">
-        <v>401</v>
-      </c>
       <c r="C318" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D318" s="3">
         <v>2026</v>
@@ -9347,13 +9347,13 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
+        <v>399</v>
+      </c>
+      <c r="B319" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="B319" s="4" t="s">
-        <v>401</v>
-      </c>
       <c r="C319" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D319" s="3">
         <v>2026</v>
@@ -9367,13 +9367,13 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
+        <v>604</v>
+      </c>
+      <c r="B320" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="B320" s="4" t="s">
+      <c r="C320" s="11" t="s">
         <v>606</v>
-      </c>
-      <c r="C320" s="11" t="s">
-        <v>607</v>
       </c>
       <c r="D320" s="3">
         <v>2026</v>
@@ -9387,13 +9387,13 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C321" s="11" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D321" s="3">
         <v>2026</v>
@@ -9407,13 +9407,13 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B322" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="C322" s="11" t="s">
         <v>609</v>
-      </c>
-      <c r="C322" s="11" t="s">
-        <v>610</v>
       </c>
       <c r="D322" s="3">
         <v>2026</v>
@@ -9427,13 +9427,13 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C323" s="11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D323" s="3">
         <v>2026</v>
@@ -9447,13 +9447,13 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B324" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="C324" s="11" t="s">
         <v>612</v>
-      </c>
-      <c r="C324" s="11" t="s">
-        <v>613</v>
       </c>
       <c r="D324" s="3">
         <v>2026</v>
@@ -9467,13 +9467,13 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C325" s="11" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D325" s="3">
         <v>2026</v>
@@ -9487,13 +9487,13 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C326" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D326" s="3">
         <v>2026</v>
@@ -9507,13 +9507,13 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C327" s="11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D327" s="3">
         <v>2026</v>
@@ -9527,13 +9527,13 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C328" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D328" s="3">
         <v>2026</v>
@@ -9547,13 +9547,13 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
+        <v>572</v>
+      </c>
+      <c r="B329" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="B329" s="4" t="s">
-        <v>574</v>
-      </c>
       <c r="C329" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D329" s="3">
         <v>2026</v>
@@ -9567,13 +9567,13 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C330" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D330" s="3">
         <v>2026</v>
@@ -9587,13 +9587,13 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C331" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D331" s="3">
         <v>2026</v>
@@ -9607,13 +9607,13 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C332" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D332" s="3">
         <v>2026</v>
@@ -9627,13 +9627,13 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C333" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D333" s="3">
         <v>2026</v>
@@ -9647,13 +9647,13 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C334" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D334" s="3">
         <v>2026</v>
@@ -9667,13 +9667,13 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B335" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C335" t="s">
         <v>513</v>
-      </c>
-      <c r="C335" t="s">
-        <v>514</v>
       </c>
       <c r="D335" s="3">
         <v>2026</v>
@@ -9687,13 +9687,13 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B336" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C336" t="s">
         <v>515</v>
-      </c>
-      <c r="C336" t="s">
-        <v>516</v>
       </c>
       <c r="D336" s="3">
         <v>2026</v>
@@ -9707,13 +9707,13 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C337" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D337" s="3">
         <v>2026</v>
@@ -9727,13 +9727,13 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B338" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="C338" t="s">
         <v>518</v>
-      </c>
-      <c r="C338" t="s">
-        <v>519</v>
       </c>
       <c r="D338" s="3">
         <v>2026</v>
@@ -9747,13 +9747,13 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C339" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D339" s="3">
         <v>2026</v>
@@ -9767,13 +9767,13 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B340" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C340" t="s">
         <v>521</v>
-      </c>
-      <c r="C340" t="s">
-        <v>522</v>
       </c>
       <c r="D340" s="3">
         <v>2026</v>
@@ -9787,13 +9787,13 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C341" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D341" s="3">
         <v>2026</v>
@@ -9807,13 +9807,13 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B342" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="C342" t="s">
         <v>529</v>
-      </c>
-      <c r="C342" t="s">
-        <v>530</v>
       </c>
       <c r="D342" s="3">
         <v>2026</v>
@@ -9827,13 +9827,13 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
+        <v>531</v>
+      </c>
+      <c r="B343" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B343" s="4" t="s">
+      <c r="C343" t="s">
         <v>533</v>
-      </c>
-      <c r="C343" t="s">
-        <v>534</v>
       </c>
       <c r="D343" s="3">
         <v>2026</v>
@@ -9847,13 +9847,13 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B344" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="C344" t="s">
         <v>535</v>
-      </c>
-      <c r="C344" t="s">
-        <v>536</v>
       </c>
       <c r="D344" s="3">
         <v>2026</v>
@@ -9867,13 +9867,13 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C345" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D345" s="3">
         <v>2026</v>
@@ -9887,13 +9887,13 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B346" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="C346" t="s">
         <v>538</v>
-      </c>
-      <c r="C346" t="s">
-        <v>539</v>
       </c>
       <c r="D346" s="3">
         <v>2026</v>
@@ -9907,13 +9907,13 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B347" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C347" t="s">
         <v>540</v>
-      </c>
-      <c r="C347" t="s">
-        <v>541</v>
       </c>
       <c r="D347" s="3">
         <v>2026</v>
@@ -9927,13 +9927,13 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B348" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="C348" t="s">
         <v>542</v>
-      </c>
-      <c r="C348" t="s">
-        <v>543</v>
       </c>
       <c r="D348" s="3">
         <v>2026</v>
@@ -9947,13 +9947,13 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B349" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C349" t="s">
         <v>508</v>
-      </c>
-      <c r="C349" t="s">
-        <v>509</v>
       </c>
       <c r="D349" s="3">
         <v>2026</v>
@@ -9967,13 +9967,13 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C350" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D350" s="3">
         <v>2026</v>
@@ -9987,13 +9987,13 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C351" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D351" s="3">
         <v>2026</v>
@@ -10007,13 +10007,13 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C352" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D352" s="3">
         <v>2026</v>
@@ -10027,13 +10027,13 @@
     </row>
     <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C353" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D353" s="3">
         <v>2026</v>
@@ -10047,13 +10047,13 @@
     </row>
     <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C354" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D354" s="3">
         <v>2026</v>
@@ -10067,13 +10067,13 @@
     </row>
     <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C355" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D355" s="3">
         <v>2026</v>
@@ -10087,13 +10087,13 @@
     </row>
     <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C356" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D356" s="3">
         <v>2026</v>
@@ -10107,13 +10107,13 @@
     </row>
     <row r="357" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C357" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D357" s="3">
         <v>2026</v>
@@ -10127,13 +10127,13 @@
     </row>
     <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C358" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D358" s="3">
         <v>2026</v>
@@ -10147,13 +10147,13 @@
     </row>
     <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C359" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D359" s="3">
         <v>2026</v>
@@ -10167,13 +10167,13 @@
     </row>
     <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C360" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D360" s="3">
         <v>2026</v>
@@ -10187,13 +10187,13 @@
     </row>
     <row r="361" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C361" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D361" s="3">
         <v>2026</v>
@@ -10207,13 +10207,13 @@
     </row>
     <row r="362" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C362" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D362" s="3">
         <v>2026</v>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="363" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C363" t="s">
         <v>12</v>
@@ -10247,13 +10247,13 @@
     </row>
     <row r="364" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C364" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D364" s="3">
         <v>2026</v>
@@ -10267,13 +10267,13 @@
     </row>
     <row r="365" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C365" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D365" s="3">
         <v>2026</v>
@@ -10290,7 +10290,7 @@
         <v>45</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C366" t="s">
         <v>47</v>
@@ -10311,7 +10311,7 @@
         <v>45</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C367" t="s">
         <v>44</v>
@@ -10377,7 +10377,7 @@
         <v>46</v>
       </c>
       <c r="C370" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D370" s="3">
         <v>2025</v>
@@ -10395,7 +10395,7 @@
         <v>45</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C371" t="s">
         <v>47</v>
@@ -10416,7 +10416,7 @@
         <v>45</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C372" t="s">
         <v>44</v>
@@ -10437,10 +10437,10 @@
         <v>45</v>
       </c>
       <c r="B373" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C373" t="s">
         <v>217</v>
-      </c>
-      <c r="C373" t="s">
-        <v>218</v>
       </c>
       <c r="D373" s="3">
         <v>2025</v>
@@ -10455,13 +10455,13 @@
     </row>
     <row r="374" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
+        <v>631</v>
+      </c>
+      <c r="B374" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="B374" s="4" t="s">
+      <c r="C374" s="12" t="s">
         <v>633</v>
-      </c>
-      <c r="C374" s="12" t="s">
-        <v>634</v>
       </c>
       <c r="D374" s="3">
         <v>2026</v>
@@ -10475,13 +10475,13 @@
     </row>
     <row r="375" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B375" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="C375" s="12" t="s">
         <v>635</v>
-      </c>
-      <c r="C375" s="12" t="s">
-        <v>636</v>
       </c>
       <c r="D375" s="3">
         <v>2026</v>
@@ -10495,13 +10495,13 @@
     </row>
     <row r="376" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C376" s="12" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D376" s="3">
         <v>2026</v>
@@ -10515,13 +10515,13 @@
     </row>
     <row r="377" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C377" s="12" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D377" s="3">
         <v>2026</v>
@@ -10535,13 +10535,13 @@
     </row>
     <row r="378" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B378" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="C378" s="12" t="s">
         <v>639</v>
-      </c>
-      <c r="C378" s="12" t="s">
-        <v>640</v>
       </c>
       <c r="D378" s="3">
         <v>2026</v>
@@ -10555,13 +10555,13 @@
     </row>
     <row r="379" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C379" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D379" s="3">
         <v>2026</v>
@@ -10575,13 +10575,13 @@
     </row>
     <row r="380" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B380" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C380" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D380" s="3">
         <v>2026</v>
@@ -10601,7 +10601,7 @@
         <v>6</v>
       </c>
       <c r="C381" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D381" s="3">
         <v>2027</v>
@@ -10622,7 +10622,7 @@
         <v>6</v>
       </c>
       <c r="C382" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D382" s="3">
         <v>2027</v>
@@ -10643,7 +10643,7 @@
         <v>6</v>
       </c>
       <c r="C383" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D383" s="3">
         <v>2027</v>
@@ -10664,7 +10664,7 @@
         <v>6</v>
       </c>
       <c r="C384" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D384" s="3">
         <v>2027</v>
@@ -10685,7 +10685,7 @@
         <v>6</v>
       </c>
       <c r="C385" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D385" s="3">
         <v>2027</v>
@@ -10706,7 +10706,7 @@
         <v>6</v>
       </c>
       <c r="C386" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D386" s="3">
         <v>2027</v>
@@ -10724,10 +10724,10 @@
         <v>5</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C387" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D387" s="3">
         <v>2026</v>
@@ -10745,10 +10745,10 @@
         <v>5</v>
       </c>
       <c r="B388" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C388" t="s">
         <v>318</v>
-      </c>
-      <c r="C388" t="s">
-        <v>319</v>
       </c>
       <c r="D388" s="3">
         <v>2026</v>
@@ -10766,10 +10766,10 @@
         <v>5</v>
       </c>
       <c r="B389" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C389" t="s">
         <v>320</v>
-      </c>
-      <c r="C389" t="s">
-        <v>321</v>
       </c>
       <c r="D389" s="3">
         <v>2027</v>
@@ -10787,10 +10787,10 @@
         <v>5</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C390" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D390" s="3">
         <v>2027</v>
@@ -10808,10 +10808,10 @@
         <v>5</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C391" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D391" s="3">
         <v>2027</v>
@@ -10829,10 +10829,10 @@
         <v>5</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C392" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D392" s="3">
         <v>2027</v>
@@ -10850,10 +10850,10 @@
         <v>5</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C393" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D393" s="3">
         <v>2027</v>
@@ -10871,10 +10871,10 @@
         <v>5</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C394" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D394" s="3">
         <v>2027</v>
@@ -10892,10 +10892,10 @@
         <v>5</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C395" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D395" s="3">
         <v>2027</v>
@@ -10913,10 +10913,10 @@
         <v>5</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C396" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D396" s="3">
         <v>2027</v>
@@ -10934,10 +10934,10 @@
         <v>5</v>
       </c>
       <c r="B397" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C397" t="s">
         <v>326</v>
-      </c>
-      <c r="C397" t="s">
-        <v>327</v>
       </c>
       <c r="D397" s="3">
         <v>2027</v>
@@ -10952,13 +10952,13 @@
     </row>
     <row r="398" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
+        <v>52</v>
+      </c>
+      <c r="B398" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B398" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="C398" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D398" s="3">
         <v>2026</v>
@@ -10973,13 +10973,13 @@
     </row>
     <row r="399" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
+        <v>52</v>
+      </c>
+      <c r="B399" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B399" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="C399" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D399" s="3">
         <v>2026</v>
@@ -10993,13 +10993,13 @@
     </row>
     <row r="400" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C400" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D400" s="3">
         <v>2026</v>
@@ -11014,13 +11014,13 @@
     </row>
     <row r="401" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C401" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D401" s="3">
         <v>2026</v>
@@ -11035,13 +11035,13 @@
     </row>
     <row r="402" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C402" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D402" s="3">
         <v>2026</v>
@@ -11056,13 +11056,13 @@
     </row>
     <row r="403" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C403" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D403" s="3">
         <v>2026</v>
@@ -11076,13 +11076,13 @@
     </row>
     <row r="404" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C404" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D404" s="3">
         <v>2026</v>
@@ -11096,13 +11096,13 @@
     </row>
     <row r="405" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C405" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D405" s="3">
         <v>2026</v>
@@ -11116,13 +11116,13 @@
     </row>
     <row r="406" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C406" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D406" s="3">
         <v>2026</v>
@@ -11136,13 +11136,13 @@
     </row>
     <row r="407" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B407" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C407" t="s">
         <v>175</v>
-      </c>
-      <c r="C407" t="s">
-        <v>176</v>
       </c>
       <c r="D407" s="3">
         <v>2026</v>
@@ -11156,13 +11156,13 @@
     </row>
     <row r="408" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C408" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D408" s="3">
         <v>2026</v>
@@ -11176,13 +11176,13 @@
     </row>
     <row r="409" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C409" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D409" s="3">
         <v>2026</v>
@@ -11196,13 +11196,13 @@
     </row>
     <row r="410" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C410" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D410" s="3">
         <v>2026</v>
@@ -11216,13 +11216,13 @@
     </row>
     <row r="411" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C411" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D411" s="3">
         <v>2026</v>
@@ -11236,10 +11236,10 @@
     </row>
     <row r="412" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C412" t="s">
         <v>12</v>
@@ -11283,7 +11283,7 @@
         <v>43</v>
       </c>
       <c r="C414" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D414" s="3">
         <v>2026</v>
@@ -11301,7 +11301,7 @@
         <v>42</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C415" t="s">
         <v>44</v>
@@ -11322,7 +11322,7 @@
         <v>42</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C416" t="s">
         <v>44</v>
@@ -11343,10 +11343,10 @@
         <v>42</v>
       </c>
       <c r="B417" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C417" t="s">
         <v>147</v>
-      </c>
-      <c r="C417" t="s">
-        <v>148</v>
       </c>
       <c r="D417" s="3">
         <v>2026</v>
@@ -11367,7 +11367,7 @@
         <v>208</v>
       </c>
       <c r="C418" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D418" s="3">
         <v>2026</v>
@@ -11387,7 +11387,7 @@
         <v>208</v>
       </c>
       <c r="C419" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D419" s="3">
         <v>2026</v>
@@ -11407,7 +11407,7 @@
         <v>208</v>
       </c>
       <c r="C420" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D420" s="3">
         <v>2026</v>
@@ -11427,7 +11427,7 @@
         <v>208</v>
       </c>
       <c r="C421" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D421" s="3">
         <v>2026</v>
@@ -11447,7 +11447,7 @@
         <v>2008</v>
       </c>
       <c r="C422" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D422" s="3">
         <v>2026</v>
@@ -11467,7 +11467,7 @@
         <v>2008</v>
       </c>
       <c r="C423" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D423" s="3">
         <v>2026</v>
@@ -11487,7 +11487,7 @@
         <v>2008</v>
       </c>
       <c r="C424" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D424" s="3">
         <v>2026</v>
@@ -11501,13 +11501,13 @@
     </row>
     <row r="425" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B425" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C425" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D425" s="3">
         <v>2024</v>
@@ -11521,13 +11521,13 @@
     </row>
     <row r="426" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B426" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C426" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D426" s="3">
         <v>2024</v>
@@ -11541,13 +11541,13 @@
     </row>
     <row r="427" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B427" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C427" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D427" s="3">
         <v>2025</v>
@@ -11561,13 +11561,13 @@
     </row>
     <row r="428" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B428" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C428" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D428" s="3">
         <v>2024</v>
@@ -11581,13 +11581,13 @@
     </row>
     <row r="429" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B429" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C429" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D429" s="3">
         <v>2024</v>
@@ -11601,13 +11601,13 @@
     </row>
     <row r="430" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B430" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C430" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D430" s="3">
         <v>2025</v>
@@ -11621,13 +11621,13 @@
     </row>
     <row r="431" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B431" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C431" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D431" s="3">
         <v>2026</v>
@@ -11641,13 +11641,13 @@
     </row>
     <row r="432" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
+        <v>482</v>
+      </c>
+      <c r="B432" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="C432" t="s">
         <v>483</v>
-      </c>
-      <c r="B432" s="10" t="s">
-        <v>555</v>
-      </c>
-      <c r="C432" t="s">
-        <v>484</v>
       </c>
       <c r="D432" s="3">
         <v>2026</v>
@@ -11661,13 +11661,13 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B433" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C433" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D433" s="3">
         <v>2026</v>
@@ -11681,13 +11681,13 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B434" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C434" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D434" s="3">
         <v>2026</v>
@@ -11701,13 +11701,13 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B435" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C435" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D435" s="3">
         <v>2026</v>
@@ -11721,13 +11721,13 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B436" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C436" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D436" s="3">
         <v>2026</v>
@@ -11741,13 +11741,13 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B437" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C437" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D437" s="3">
         <v>2026</v>
@@ -11761,10 +11761,10 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C438" t="s">
         <v>13</v>
@@ -11781,13 +11781,13 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B439" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C439" t="s">
         <v>486</v>
-      </c>
-      <c r="C439" t="s">
-        <v>487</v>
       </c>
       <c r="D439" s="3">
         <v>2026</v>
@@ -11801,13 +11801,13 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C440" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D440" s="3">
         <v>2027</v>
@@ -11821,13 +11821,13 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B441" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C441" t="s">
         <v>502</v>
-      </c>
-      <c r="C441" t="s">
-        <v>503</v>
       </c>
       <c r="D441" s="3">
         <v>2027</v>
@@ -11841,13 +11841,13 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C442" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D442" s="3">
         <v>2026</v>
@@ -11861,13 +11861,13 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B443" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C443" t="s">
         <v>504</v>
-      </c>
-      <c r="C443" t="s">
-        <v>505</v>
       </c>
       <c r="D443" s="3">
         <v>2026</v>
@@ -11881,13 +11881,13 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C444" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D444" s="3">
         <v>2026</v>
@@ -11901,13 +11901,13 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C445" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D445" s="3">
         <v>2026</v>
@@ -11921,13 +11921,13 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C446" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D446" s="3">
         <v>2026</v>
@@ -11941,13 +11941,13 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
+        <v>577</v>
+      </c>
+      <c r="B447" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="B447" s="4" t="s">
+      <c r="C447" s="11" t="s">
         <v>579</v>
-      </c>
-      <c r="C447" s="11" t="s">
-        <v>580</v>
       </c>
       <c r="D447" s="3">
         <v>2026</v>
@@ -11961,13 +11961,13 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
+        <v>577</v>
+      </c>
+      <c r="B448" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="B448" s="4" t="s">
-        <v>579</v>
-      </c>
       <c r="C448" s="11" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D448" s="3">
         <v>2026</v>
@@ -11981,13 +11981,13 @@
     </row>
     <row r="449" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
+        <v>577</v>
+      </c>
+      <c r="B449" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="B449" s="4" t="s">
-        <v>579</v>
-      </c>
       <c r="C449" s="11" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D449" s="3">
         <v>2026</v>
@@ -12001,13 +12001,13 @@
     </row>
     <row r="450" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B450" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C450" s="11" t="s">
         <v>583</v>
-      </c>
-      <c r="C450" s="11" t="s">
-        <v>584</v>
       </c>
       <c r="D450" s="3">
         <v>2026</v>
@@ -12021,13 +12021,13 @@
     </row>
     <row r="451" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C451" s="11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D451" s="3">
         <v>2026</v>
@@ -12041,13 +12041,13 @@
     </row>
     <row r="452" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C452" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D452" s="3">
         <v>2026</v>
@@ -12061,13 +12061,13 @@
     </row>
     <row r="453" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C453" s="11" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D453" s="3">
         <v>2026</v>
@@ -12081,13 +12081,13 @@
     </row>
     <row r="454" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C454" s="11" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D454" s="3">
         <v>2026</v>
@@ -12101,13 +12101,13 @@
     </row>
     <row r="455" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B455" s="10">
         <v>1500</v>
       </c>
       <c r="C455" s="11" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D455" s="3">
         <v>2026</v>
@@ -12121,13 +12121,13 @@
     </row>
     <row r="456" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B456" s="10">
         <v>2500</v>
       </c>
       <c r="C456" s="11" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D456" s="3">
         <v>2026</v>
@@ -12141,13 +12141,13 @@
     </row>
     <row r="457" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B457" s="10">
         <v>3500</v>
       </c>
       <c r="C457" s="11" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D457" s="3">
         <v>2026</v>
@@ -12161,13 +12161,13 @@
     </row>
     <row r="458" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B458" s="10">
         <v>3500</v>
       </c>
       <c r="C458" s="11" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D458" s="3">
         <v>2026</v>
@@ -12181,13 +12181,13 @@
     </row>
     <row r="459" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
+        <v>68</v>
+      </c>
+      <c r="B459" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B459" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="C459" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D459" s="3">
         <v>2026</v>
@@ -12202,13 +12202,13 @@
     </row>
     <row r="460" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
+        <v>68</v>
+      </c>
+      <c r="B460" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B460" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="C460" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D460" s="3">
         <v>2026</v>
@@ -12223,13 +12223,13 @@
     </row>
     <row r="461" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
+        <v>68</v>
+      </c>
+      <c r="B461" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B461" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="C461" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D461" s="3">
         <v>2026</v>
@@ -12244,13 +12244,13 @@
     </row>
     <row r="462" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B462" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C462" t="s">
         <v>71</v>
-      </c>
-      <c r="C462" t="s">
-        <v>72</v>
       </c>
       <c r="D462" s="3">
         <v>2026</v>
@@ -12264,13 +12264,13 @@
     </row>
     <row r="463" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C463" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D463" s="3">
         <v>2026</v>
@@ -12284,13 +12284,13 @@
     </row>
     <row r="464" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C464" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D464" s="3">
         <v>2026</v>
@@ -12304,13 +12304,13 @@
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C465" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D465" s="3">
         <v>2026</v>
@@ -12324,13 +12324,13 @@
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C466" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D466" s="3">
         <v>2026</v>
@@ -12344,13 +12344,13 @@
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C467" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D467" s="3">
         <v>2026</v>
@@ -12364,13 +12364,13 @@
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C468" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D468" s="3">
         <v>2026</v>
@@ -12384,13 +12384,13 @@
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C469" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D469" s="3">
         <v>2026</v>
@@ -12404,13 +12404,13 @@
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C470" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D470" s="3">
         <v>2026</v>
@@ -12424,13 +12424,13 @@
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C471" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D471" s="3">
         <v>2026</v>
@@ -12444,13 +12444,13 @@
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C472" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D472" s="3">
         <v>2026</v>
@@ -12464,13 +12464,13 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C473" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D473" s="3">
         <v>2026</v>
@@ -12484,13 +12484,13 @@
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C474" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D474" s="3">
         <v>2026</v>
@@ -12504,13 +12504,13 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C475" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D475" s="3">
         <v>2026</v>
@@ -12524,10 +12524,10 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C476" t="s">
         <v>19</v>
@@ -12544,13 +12544,13 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B477" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C477" t="s">
         <v>237</v>
-      </c>
-      <c r="C477" t="s">
-        <v>238</v>
       </c>
       <c r="D477" s="3">
         <v>2026</v>
@@ -12564,13 +12564,13 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C478" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D478" s="3">
         <v>2026</v>
@@ -12584,13 +12584,13 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
+        <v>569</v>
+      </c>
+      <c r="B479" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="B479" s="4" t="s">
+      <c r="C479" s="11" t="s">
         <v>571</v>
-      </c>
-      <c r="C479" s="11" t="s">
-        <v>572</v>
       </c>
       <c r="D479" s="3">
         <v>2026</v>
@@ -12604,13 +12604,13 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
+        <v>566</v>
+      </c>
+      <c r="B480" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="B480" s="4" t="s">
+      <c r="C480" s="11" t="s">
         <v>568</v>
-      </c>
-      <c r="C480" s="11" t="s">
-        <v>569</v>
       </c>
       <c r="D480" s="3">
         <v>2026</v>
@@ -12624,13 +12624,13 @@
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
+        <v>125</v>
+      </c>
+      <c r="B481" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B481" s="4" t="s">
+      <c r="C481" t="s">
         <v>127</v>
-      </c>
-      <c r="C481" t="s">
-        <v>128</v>
       </c>
       <c r="D481" s="3">
         <v>2026</v>
@@ -12642,18 +12642,18 @@
         <v>177590</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
+        <v>125</v>
+      </c>
+      <c r="B482" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B482" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="C482" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D482" s="3">
         <v>2026</v>
@@ -12665,18 +12665,18 @@
         <v>206790</v>
       </c>
       <c r="G482" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
+        <v>125</v>
+      </c>
+      <c r="B483" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B483" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="C483" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D483" s="3">
         <v>2026</v>
@@ -12688,18 +12688,18 @@
         <v>194790</v>
       </c>
       <c r="G483" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
+        <v>125</v>
+      </c>
+      <c r="B484" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B484" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="C484" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D484" s="3">
         <v>2026</v>
@@ -12711,21 +12711,21 @@
         <v>210090</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
+        <v>125</v>
+      </c>
+      <c r="B485" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B485" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="C485" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D485" s="3">
         <v>2026</v>
@@ -12737,18 +12737,18 @@
         <v>206790</v>
       </c>
       <c r="G485" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C486" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D486" s="3">
         <v>2026</v>
@@ -12762,13 +12762,13 @@
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B487" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C487" t="s">
         <v>130</v>
-      </c>
-      <c r="C487" t="s">
-        <v>131</v>
       </c>
       <c r="D487" s="3">
         <v>2026</v>
@@ -12782,13 +12782,13 @@
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C488" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D488" s="3">
         <v>2026</v>
@@ -12802,13 +12802,13 @@
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C489" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D489" s="3">
         <v>2026</v>
@@ -12822,13 +12822,13 @@
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C490" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D490" s="3">
         <v>2026</v>
@@ -12842,13 +12842,13 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C491" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D491" s="3">
         <v>2026</v>
@@ -12862,13 +12862,13 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C492" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D492" s="3">
         <v>2026</v>
@@ -12882,13 +12882,13 @@
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C493" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D493" s="3">
         <v>2026</v>
@@ -12902,13 +12902,13 @@
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B494" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C494" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D494" s="3">
         <v>2026</v>
@@ -12922,13 +12922,13 @@
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B495" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C495" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D495" s="3">
         <v>2026</v>
@@ -12942,13 +12942,13 @@
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C496" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D496" s="3">
         <v>2026</v>
@@ -12962,13 +12962,13 @@
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C497" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D497" s="3">
         <v>2026</v>
@@ -12982,13 +12982,13 @@
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C498" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D498" s="3">
         <v>2026</v>
@@ -13002,13 +13002,13 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C499" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D499" s="3">
         <v>2026</v>
@@ -13022,13 +13022,13 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C500" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D500" s="3">
         <v>2026</v>
@@ -13042,13 +13042,13 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C501" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D501" s="3">
         <v>2026</v>
@@ -13062,13 +13062,13 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B502" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C502" t="s">
         <v>255</v>
-      </c>
-      <c r="C502" t="s">
-        <v>256</v>
       </c>
       <c r="D502" s="3">
         <v>2026</v>
@@ -13082,13 +13082,13 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B503" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C503" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D503" s="3">
         <v>2026</v>
@@ -13102,13 +13102,13 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C504" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D504" s="3">
         <v>2026</v>
@@ -13122,13 +13122,13 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B505" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C505" t="s">
         <v>134</v>
-      </c>
-      <c r="C505" t="s">
-        <v>135</v>
       </c>
       <c r="D505" s="3">
         <v>2026</v>
@@ -13142,13 +13142,13 @@
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C506" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D506" s="3">
         <v>2026</v>
@@ -13162,13 +13162,13 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C507" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D507" s="3">
         <v>2026</v>
@@ -13182,13 +13182,13 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C508" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D508" s="3">
         <v>2026</v>
@@ -13202,13 +13202,13 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B509" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C509" t="s">
         <v>143</v>
-      </c>
-      <c r="C509" t="s">
-        <v>144</v>
       </c>
       <c r="D509" s="3">
         <v>2026</v>
@@ -13222,13 +13222,13 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B510" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C510" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D510" s="3">
         <v>2026</v>
@@ -13242,13 +13242,13 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B511" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C511" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D511" s="3">
         <v>2026</v>
@@ -13262,13 +13262,13 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B512" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C512" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D512" s="3">
         <v>2026</v>
@@ -13282,13 +13282,13 @@
     </row>
     <row r="513" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B513" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C513" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D513" s="3">
         <v>2026</v>
@@ -13302,13 +13302,13 @@
     </row>
     <row r="514" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C514" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D514" s="3">
         <v>2026</v>
@@ -13349,7 +13349,7 @@
         <v>10</v>
       </c>
       <c r="C516" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D516" s="3">
         <v>2026</v>
@@ -13370,7 +13370,7 @@
         <v>10</v>
       </c>
       <c r="C517" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D517" s="3">
         <v>2026</v>
@@ -13391,7 +13391,7 @@
         <v>10</v>
       </c>
       <c r="C518" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D518" s="3">
         <v>2026</v>
@@ -13412,7 +13412,7 @@
         <v>10</v>
       </c>
       <c r="C519" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D519" s="3">
         <v>2026</v>
@@ -13433,7 +13433,7 @@
         <v>10</v>
       </c>
       <c r="C520" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D520" s="3">
         <v>2026</v>
@@ -13451,10 +13451,10 @@
         <v>7</v>
       </c>
       <c r="B521" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C521" t="s">
         <v>66</v>
-      </c>
-      <c r="C521" t="s">
-        <v>67</v>
       </c>
       <c r="D521" s="3">
         <v>2027</v>
@@ -13472,7 +13472,7 @@
         <v>7</v>
       </c>
       <c r="B522" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C522" t="s">
         <v>11</v>
@@ -13493,10 +13493,10 @@
         <v>7</v>
       </c>
       <c r="B523" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C523" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D523" s="3">
         <v>2026</v>
@@ -13513,10 +13513,10 @@
         <v>7</v>
       </c>
       <c r="B524" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C524" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D524" s="3">
         <v>2026</v>
@@ -13533,10 +13533,10 @@
         <v>7</v>
       </c>
       <c r="B525" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C525" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D525" s="3">
         <v>2026</v>
@@ -13553,10 +13553,10 @@
         <v>7</v>
       </c>
       <c r="B526" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C526" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D526" s="3">
         <v>2027</v>
@@ -13574,10 +13574,10 @@
         <v>7</v>
       </c>
       <c r="B527" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C527" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D527" s="3">
         <v>2027</v>
@@ -13595,10 +13595,10 @@
         <v>7</v>
       </c>
       <c r="B528" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C528" t="s">
         <v>136</v>
-      </c>
-      <c r="C528" t="s">
-        <v>137</v>
       </c>
       <c r="D528" s="3">
         <v>2026</v>
@@ -13615,10 +13615,10 @@
         <v>7</v>
       </c>
       <c r="B529" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C529" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D529" s="3">
         <v>2026</v>
@@ -13635,10 +13635,10 @@
         <v>7</v>
       </c>
       <c r="B530" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C530" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D530" s="3">
         <v>2026</v>
@@ -13655,10 +13655,10 @@
         <v>7</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C531" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D531" s="3">
         <v>2026</v>
@@ -13675,10 +13675,10 @@
         <v>7</v>
       </c>
       <c r="B532" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C532" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D532" s="3">
         <v>2026</v>
@@ -13695,10 +13695,10 @@
         <v>7</v>
       </c>
       <c r="B533" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C533" t="s">
         <v>140</v>
-      </c>
-      <c r="C533" t="s">
-        <v>141</v>
       </c>
       <c r="D533" s="3">
         <v>2026</v>
@@ -13715,10 +13715,10 @@
         <v>7</v>
       </c>
       <c r="B534" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C534" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D534" s="3">
         <v>2026</v>
@@ -13735,10 +13735,10 @@
         <v>7</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C535" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D535" s="3">
         <v>2026</v>
@@ -13755,7 +13755,7 @@
         <v>7</v>
       </c>
       <c r="B536" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C536" t="s">
         <v>47</v>
@@ -13775,10 +13775,10 @@
         <v>7</v>
       </c>
       <c r="B537" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C537" t="s">
         <v>432</v>
-      </c>
-      <c r="C537" t="s">
-        <v>433</v>
       </c>
       <c r="D537" s="3">
         <v>2026</v>
@@ -13795,10 +13795,10 @@
         <v>7</v>
       </c>
       <c r="B538" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C538" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D538" s="3">
         <v>2026</v>
@@ -13815,10 +13815,10 @@
         <v>7</v>
       </c>
       <c r="B539" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C539" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D539" s="3">
         <v>2026</v>
@@ -13835,10 +13835,10 @@
         <v>7</v>
       </c>
       <c r="B540" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C540" t="s">
         <v>442</v>
-      </c>
-      <c r="C540" t="s">
-        <v>443</v>
       </c>
       <c r="D540" s="3">
         <v>2027</v>
@@ -13855,10 +13855,10 @@
         <v>7</v>
       </c>
       <c r="B541" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C541" t="s">
         <v>445</v>
-      </c>
-      <c r="C541" t="s">
-        <v>446</v>
       </c>
       <c r="D541" s="3">
         <v>2026</v>
@@ -13875,10 +13875,10 @@
         <v>7</v>
       </c>
       <c r="B542" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C542" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D542" s="3">
         <v>2026</v>
@@ -13895,10 +13895,10 @@
         <v>7</v>
       </c>
       <c r="B543" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C543" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D543" s="3">
         <v>2026</v>
@@ -13915,10 +13915,10 @@
         <v>7</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C544" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D544" s="3">
         <v>2026</v>
@@ -13932,13 +13932,13 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
+        <v>543</v>
+      </c>
+      <c r="B545" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="B545" s="4" t="s">
-        <v>545</v>
-      </c>
       <c r="C545" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D545" s="3">
         <v>2026</v>
@@ -13952,13 +13952,13 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B546" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C546" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D546" s="3">
         <v>2026</v>
@@ -13972,10 +13972,10 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C547" t="s">
         <v>41</v>
@@ -13992,10 +13992,10 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B548" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C548" t="s">
         <v>41</v>
@@ -14012,10 +14012,10 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B549" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C549" t="s">
         <v>41</v>
@@ -14032,10 +14032,10 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B550" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C550" t="s">
         <v>41</v>
@@ -14052,10 +14052,10 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B551" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C551" t="s">
         <v>41</v>
@@ -14072,13 +14072,13 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
+        <v>551</v>
+      </c>
+      <c r="B552" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="B552" s="10" t="s">
-        <v>553</v>
-      </c>
       <c r="C552" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D552" s="3">
         <v>2026</v>
@@ -14092,13 +14092,13 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B553" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C553" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D553" s="3">
         <v>2026</v>
@@ -14112,13 +14112,13 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B554" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C554" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D554" s="3">
         <v>2026</v>
@@ -14132,13 +14132,13 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
+        <v>651</v>
+      </c>
+      <c r="B555" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="B555" s="4" t="s">
+      <c r="C555" t="s">
         <v>653</v>
-      </c>
-      <c r="C555" t="s">
-        <v>654</v>
       </c>
       <c r="D555" s="3">
         <v>2027</v>
@@ -14152,13 +14152,13 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
+        <v>651</v>
+      </c>
+      <c r="B556" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="B556" s="4" t="s">
-        <v>653</v>
-      </c>
       <c r="C556" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D556" s="3">
         <v>2027</v>
@@ -14172,16 +14172,16 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B557" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C557" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E557" t="s">
         <v>17</v>

--- a/lista_carros.xlsx
+++ b/lista_carros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA17A73-0724-4DC4-A0EE-7D4DA9D4D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D9F073-1741-4A19-8FE9-BCF84A1D18C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26388" yWindow="5220" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3472,7 +3472,7 @@
         <v>17</v>
       </c>
       <c r="F47" s="1">
-        <v>159990</v>
+        <v>164990</v>
       </c>
       <c r="O47" s="1"/>
     </row>

--- a/lista_carros.xlsx
+++ b/lista_carros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D9F073-1741-4A19-8FE9-BCF84A1D18C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D659AB6-A40A-4884-8AF4-534DF3405488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26388" yWindow="5220" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25308" yWindow="4608" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carros" sheetId="1" r:id="rId1"/>
@@ -7309,7 +7309,7 @@
         <v>213</v>
       </c>
       <c r="C218" t="s">
-        <v>61</v>
+        <v>214</v>
       </c>
       <c r="D218" s="3">
         <v>2026</v>
@@ -7318,7 +7318,7 @@
         <v>17</v>
       </c>
       <c r="F218" s="1">
-        <v>0</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.3">
